--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany 2. Bundesliga_20242025.xlsx
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,19 +2873,19 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -3085,25 +3085,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
@@ -3306,22 +3306,22 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AU13" t="n">
         <v>5</v>
@@ -3521,25 +3521,25 @@
         <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -3739,25 +3739,25 @@
         <v>1.85</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1.53</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU15" t="n">
         <v>5</v>
@@ -3957,25 +3957,25 @@
         <v>1.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
@@ -4175,25 +4175,25 @@
         <v>1.92</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU17" t="n">
         <v>6</v>
@@ -4396,22 +4396,22 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS18" t="n">
         <v>1.82</v>
       </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -4614,22 +4614,22 @@
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
@@ -4829,25 +4829,25 @@
         <v>2.17</v>
       </c>
       <c r="AN20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
         <v>1</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
@@ -5047,25 +5047,25 @@
         <v>1.55</v>
       </c>
       <c r="AN21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AU21" t="n">
         <v>3</v>
@@ -5265,25 +5265,25 @@
         <v>1.47</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.42</v>
+        <v>2.77</v>
       </c>
       <c r="AU22" t="n">
         <v>6</v>
@@ -5483,25 +5483,25 @@
         <v>1.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="n">
         <v>3</v>
@@ -5701,25 +5701,25 @@
         <v>2.15</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.07</v>
+        <v>0.86</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
@@ -5919,25 +5919,25 @@
         <v>2.55</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.41</v>
+        <v>3.71</v>
       </c>
       <c r="AU25" t="n">
         <v>13</v>
@@ -6140,22 +6140,22 @@
         <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="AU26" t="n">
         <v>8</v>
@@ -6358,22 +6358,22 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -6573,25 +6573,25 @@
         <v>1.57</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
@@ -6791,25 +6791,25 @@
         <v>1.67</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO29" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AU29" t="n">
         <v>5</v>
@@ -7009,25 +7009,25 @@
         <v>1.38</v>
       </c>
       <c r="AN30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO30" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="AU30" t="n">
         <v>6</v>
@@ -7227,25 +7227,25 @@
         <v>2.95</v>
       </c>
       <c r="AN31" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -7445,25 +7445,25 @@
         <v>1.54</v>
       </c>
       <c r="AN32" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS32" t="n">
         <v>1.58</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AU32" t="n">
         <v>5</v>
@@ -7663,25 +7663,25 @@
         <v>1.45</v>
       </c>
       <c r="AN33" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO33" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.97</v>
+        <v>1.48</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AU33" t="n">
         <v>3</v>
@@ -7881,25 +7881,25 @@
         <v>1.62</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AO34" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="AU34" t="n">
         <v>10</v>
@@ -8099,25 +8099,25 @@
         <v>2.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.96</v>
+        <v>1.33</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AU35" t="n">
         <v>1</v>
@@ -8317,25 +8317,25 @@
         <v>1.41</v>
       </c>
       <c r="AN36" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO36" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AS36" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="AU36" t="n">
         <v>5</v>
@@ -8538,22 +8538,22 @@
         <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="AP37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR37" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AS37" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="AU37" t="n">
         <v>1</v>
@@ -8753,25 +8753,25 @@
         <v>1.36</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO38" t="n">
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="AU38" t="n">
         <v>4</v>
@@ -8971,25 +8971,25 @@
         <v>2</v>
       </c>
       <c r="AN39" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AO39" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="AU39" t="n">
         <v>5</v>
@@ -9189,25 +9189,25 @@
         <v>1.85</v>
       </c>
       <c r="AN40" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AO40" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="AU40" t="n">
         <v>9</v>
@@ -9407,25 +9407,25 @@
         <v>1.6</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AO41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.41</v>
+        <v>2.09</v>
       </c>
       <c r="AU41" t="n">
         <v>3</v>
@@ -9625,25 +9625,25 @@
         <v>2</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AU42" t="n">
         <v>3</v>
@@ -9843,25 +9843,25 @@
         <v>2.65</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="AU43" t="n">
         <v>13</v>
@@ -10064,22 +10064,22 @@
         <v>2</v>
       </c>
       <c r="AO44" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="AU44" t="n">
         <v>2</v>
@@ -10279,25 +10279,25 @@
         <v>1.5</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AO45" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP45" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AU45" t="n">
         <v>5</v>
@@ -10497,25 +10497,25 @@
         <v>3.25</v>
       </c>
       <c r="AN46" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO46" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AU46" t="n">
         <v>8</v>
@@ -10715,25 +10715,25 @@
         <v>1.69</v>
       </c>
       <c r="AN47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO47" t="n">
         <v>2</v>
       </c>
-      <c r="AO47" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AP47" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.96</v>
+        <v>1.29</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AU47" t="n">
         <v>5</v>
@@ -10933,25 +10933,25 @@
         <v>2.05</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO48" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AP48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ48" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ48" t="n">
-        <v>0.82</v>
-      </c>
       <c r="AR48" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AS48" t="n">
         <v>1.46</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="AU48" t="n">
         <v>7</v>
@@ -11151,25 +11151,25 @@
         <v>1.38</v>
       </c>
       <c r="AN49" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AO49" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AU49" t="n">
         <v>5</v>
@@ -11369,25 +11369,25 @@
         <v>1.38</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO50" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="AU50" t="n">
         <v>3</v>
@@ -11587,25 +11587,25 @@
         <v>1.72</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AO51" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AU51" t="n">
         <v>9</v>
@@ -11805,25 +11805,25 @@
         <v>1.35</v>
       </c>
       <c r="AN52" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO52" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.86</v>
+        <v>1.41</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="AU52" t="n">
         <v>4</v>
@@ -12023,25 +12023,25 @@
         <v>1.85</v>
       </c>
       <c r="AN53" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AO53" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AS53" t="n">
-        <v>0.93</v>
+        <v>1.19</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AU53" t="n">
         <v>4</v>
@@ -12241,25 +12241,25 @@
         <v>1.42</v>
       </c>
       <c r="AN54" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="AO54" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.74</v>
+        <v>1.39</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AU54" t="n">
         <v>4</v>
@@ -12459,25 +12459,25 @@
         <v>1.55</v>
       </c>
       <c r="AN55" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AU55" t="n">
         <v>4</v>
@@ -12677,25 +12677,25 @@
         <v>1.56</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO56" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP56" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AU56" t="n">
         <v>6</v>
@@ -12895,25 +12895,25 @@
         <v>1.35</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AO57" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR57" t="n">
         <v>1.36</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="AU57" t="n">
         <v>1</v>
@@ -13113,25 +13113,25 @@
         <v>2</v>
       </c>
       <c r="AN58" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="AO58" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AU58" t="n">
         <v>9</v>
@@ -13331,25 +13331,25 @@
         <v>1.33</v>
       </c>
       <c r="AN59" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO59" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AP59" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS59" t="n">
         <v>1.35</v>
       </c>
-      <c r="AQ59" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AT59" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AU59" t="n">
         <v>2</v>
@@ -13549,25 +13549,25 @@
         <v>1.65</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="AO60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.61</v>
+        <v>2.83</v>
       </c>
       <c r="AU60" t="n">
         <v>7</v>
@@ -13767,25 +13767,25 @@
         <v>1.4</v>
       </c>
       <c r="AN61" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO61" t="n">
         <v>0.67</v>
       </c>
-      <c r="AO61" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AP61" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AQ61" t="n">
         <v>1.12</v>
       </c>
-      <c r="AQ61" t="n">
-        <v>1</v>
-      </c>
       <c r="AR61" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AT61" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AU61" t="n">
         <v>3</v>
@@ -13985,25 +13985,25 @@
         <v>2.3</v>
       </c>
       <c r="AN62" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO62" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AU62" t="n">
         <v>5</v>
@@ -14203,25 +14203,25 @@
         <v>2</v>
       </c>
       <c r="AN63" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AO63" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AP63" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="AU63" t="n">
         <v>6</v>
@@ -14421,25 +14421,25 @@
         <v>2.2</v>
       </c>
       <c r="AN64" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO64" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AS64" t="n">
-        <v>0.96</v>
+        <v>1.23</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AU64" t="n">
         <v>5</v>
@@ -14639,25 +14639,25 @@
         <v>2.8</v>
       </c>
       <c r="AN65" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO65" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AS65" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
       <c r="AT65" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AU65" t="n">
         <v>9</v>
@@ -14857,25 +14857,25 @@
         <v>2.05</v>
       </c>
       <c r="AN66" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="AO66" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AS66" t="n">
         <v>1.49</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="AU66" t="n">
         <v>5</v>
@@ -15075,25 +15075,25 @@
         <v>3.3</v>
       </c>
       <c r="AN67" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AO67" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.24</v>
+        <v>3.31</v>
       </c>
       <c r="AU67" t="n">
         <v>4</v>
@@ -15293,25 +15293,25 @@
         <v>1.57</v>
       </c>
       <c r="AN68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS68" t="n">
         <v>1.33</v>
       </c>
-      <c r="AO68" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AT68" t="n">
-        <v>2.33</v>
+        <v>2.49</v>
       </c>
       <c r="AU68" t="n">
         <v>4</v>
@@ -15514,22 +15514,22 @@
         <v>1</v>
       </c>
       <c r="AO69" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR69" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AU69" t="n">
         <v>7</v>
@@ -15732,22 +15732,22 @@
         <v>1</v>
       </c>
       <c r="AO70" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AT70" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="AU70" t="n">
         <v>1</v>
@@ -15947,25 +15947,25 @@
         <v>1.8</v>
       </c>
       <c r="AN71" t="n">
-        <v>1</v>
+        <v>2.14</v>
       </c>
       <c r="AO71" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP71" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR71" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ71" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AR71" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AS71" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="AU71" t="n">
         <v>3</v>
@@ -16165,25 +16165,25 @@
         <v>1.4</v>
       </c>
       <c r="AN72" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AO72" t="n">
-        <v>0.33</v>
+        <v>1.86</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AU72" t="n">
         <v>9</v>
@@ -16383,25 +16383,25 @@
         <v>1.56</v>
       </c>
       <c r="AN73" t="n">
-        <v>1.67</v>
+        <v>2.43</v>
       </c>
       <c r="AO73" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="AU73" t="n">
         <v>11</v>
@@ -16601,25 +16601,25 @@
         <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AO74" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AT74" t="n">
-        <v>3.4</v>
+        <v>3.51</v>
       </c>
       <c r="AU74" t="n">
         <v>1</v>
@@ -16819,25 +16819,25 @@
         <v>2</v>
       </c>
       <c r="AN75" t="n">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="AO75" t="n">
-        <v>0.25</v>
+        <v>0.88</v>
       </c>
       <c r="AP75" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="AT75" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AU75" t="n">
         <v>5</v>
@@ -17037,25 +17037,25 @@
         <v>1.57</v>
       </c>
       <c r="AN76" t="n">
-        <v>0.5</v>
+        <v>0.63</v>
       </c>
       <c r="AO76" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="AU76" t="n">
         <v>1</v>
@@ -17255,22 +17255,22 @@
         <v>0</v>
       </c>
       <c r="AN77" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO77" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.13</v>
+        <v>0.99</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AT77" t="n">
         <v>2.26</v>
@@ -17473,25 +17473,25 @@
         <v>2.05</v>
       </c>
       <c r="AN78" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="AO78" t="n">
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AU78" t="n">
         <v>3</v>
@@ -17691,25 +17691,25 @@
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>0.67</v>
+        <v>1.13</v>
       </c>
       <c r="AO79" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="AU79" t="n">
         <v>8</v>
@@ -17909,25 +17909,25 @@
         <v>1.36</v>
       </c>
       <c r="AN80" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="AO80" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP80" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AU80" t="n">
         <v>2</v>
@@ -18130,22 +18130,22 @@
         <v>1.25</v>
       </c>
       <c r="AO81" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AU81" t="n">
         <v>4</v>
@@ -18345,25 +18345,25 @@
         <v>2.25</v>
       </c>
       <c r="AN82" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO82" t="n">
         <v>2</v>
       </c>
-      <c r="AO82" t="n">
-        <v>3</v>
-      </c>
       <c r="AP82" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="AU82" t="n">
         <v>2</v>
@@ -18563,25 +18563,25 @@
         <v>2.15</v>
       </c>
       <c r="AN83" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AO83" t="n">
-        <v>1.2</v>
+        <v>1.78</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR83" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AT83" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="AU83" t="n">
         <v>3</v>
@@ -18781,25 +18781,25 @@
         <v>2.03</v>
       </c>
       <c r="AN84" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AO84" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AS84" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AU84" t="n">
         <v>13</v>
@@ -18999,25 +18999,25 @@
         <v>1.76</v>
       </c>
       <c r="AN85" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AO85" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.96</v>
+        <v>2.67</v>
       </c>
       <c r="AU85" t="n">
         <v>2</v>
@@ -19217,25 +19217,25 @@
         <v>1.85</v>
       </c>
       <c r="AN86" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AO86" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.71</v>
+        <v>2.51</v>
       </c>
       <c r="AU86" t="n">
         <v>6</v>
@@ -19435,25 +19435,25 @@
         <v>1.33</v>
       </c>
       <c r="AN87" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AO87" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR87" t="n">
         <v>1.2</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AU87" t="n">
         <v>10</v>
@@ -19653,25 +19653,25 @@
         <v>2.05</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.25</v>
+        <v>2.22</v>
       </c>
       <c r="AO88" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ88" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR88" t="n">
         <v>1.24</v>
       </c>
-      <c r="AR88" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AS88" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AT88" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="AU88" t="n">
         <v>7</v>
@@ -19874,22 +19874,22 @@
         <v>1</v>
       </c>
       <c r="AO89" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AS89" t="n">
-        <v>0.93</v>
+        <v>1.16</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="AU89" t="n">
         <v>5</v>
@@ -20089,25 +20089,25 @@
         <v>1.48</v>
       </c>
       <c r="AN90" t="n">
-        <v>1</v>
+        <v>1.78</v>
       </c>
       <c r="AO90" t="n">
-        <v>0.25</v>
+        <v>1.78</v>
       </c>
       <c r="AP90" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ90" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR90" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ90" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AR90" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AS90" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AT90" t="n">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="AU90" t="n">
         <v>5</v>
@@ -20307,25 +20307,25 @@
         <v>1.75</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.5</v>
+        <v>0.78</v>
       </c>
       <c r="AO91" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="AU91" t="n">
         <v>2</v>
@@ -20525,25 +20525,25 @@
         <v>1.3</v>
       </c>
       <c r="AN92" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="AO92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.26</v>
+        <v>2.49</v>
       </c>
       <c r="AU92" t="n">
         <v>4</v>
@@ -20743,25 +20743,25 @@
         <v>1.52</v>
       </c>
       <c r="AN93" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AO93" t="n">
         <v>0.8</v>
       </c>
       <c r="AP93" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="AU93" t="n">
         <v>5</v>
@@ -20961,25 +20961,25 @@
         <v>1.25</v>
       </c>
       <c r="AN94" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AO94" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AU94" t="n">
         <v>2</v>
@@ -21179,25 +21179,25 @@
         <v>1.57</v>
       </c>
       <c r="AN95" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AO95" t="n">
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AU95" t="n">
         <v>5</v>
@@ -21397,25 +21397,25 @@
         <v>1.77</v>
       </c>
       <c r="AN96" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="AO96" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AU96" t="n">
         <v>8</v>
@@ -21615,25 +21615,25 @@
         <v>1.4</v>
       </c>
       <c r="AN97" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO97" t="n">
         <v>1.2</v>
       </c>
-      <c r="AO97" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AP97" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AS97" t="n">
         <v>1.82</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
       <c r="AU97" t="n">
         <v>4</v>
@@ -21833,25 +21833,25 @@
         <v>1.65</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AO98" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AU98" t="n">
         <v>6</v>
@@ -22051,25 +22051,25 @@
         <v>2.15</v>
       </c>
       <c r="AN99" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AO99" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AS99" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AU99" t="n">
         <v>2</v>
@@ -22269,25 +22269,25 @@
         <v>2.5</v>
       </c>
       <c r="AN100" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AO100" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AU100" t="n">
         <v>4</v>
@@ -22487,25 +22487,25 @@
         <v>1.3</v>
       </c>
       <c r="AN101" t="n">
-        <v>1.4</v>
+        <v>0.82</v>
       </c>
       <c r="AO101" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="AU101" t="n">
         <v>4</v>
@@ -22705,25 +22705,25 @@
         <v>1.57</v>
       </c>
       <c r="AN102" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AO102" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="AU102" t="n">
         <v>5</v>
@@ -22923,25 +22923,25 @@
         <v>2.9</v>
       </c>
       <c r="AN103" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AO103" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.22</v>
+        <v>3.09</v>
       </c>
       <c r="AU103" t="n">
         <v>1</v>
@@ -23141,22 +23141,22 @@
         <v>1.62</v>
       </c>
       <c r="AN104" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AO104" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AT104" t="n">
         <v>2.81</v>
@@ -23359,25 +23359,25 @@
         <v>1.93</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.8</v>
+        <v>1.55</v>
       </c>
       <c r="AO105" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AS105" t="n">
-        <v>0.9</v>
+        <v>1.16</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU105" t="n">
         <v>8</v>
@@ -23577,25 +23577,25 @@
         <v>1.67</v>
       </c>
       <c r="AN106" t="n">
-        <v>1</v>
+        <v>1.82</v>
       </c>
       <c r="AO106" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.73</v>
+        <v>2.57</v>
       </c>
       <c r="AU106" t="n">
         <v>3</v>
@@ -23795,25 +23795,25 @@
         <v>2.2</v>
       </c>
       <c r="AN107" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AO107" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AU107" t="n">
         <v>2</v>
@@ -24013,25 +24013,25 @@
         <v>2.45</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AO108" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AU108" t="n">
         <v>4</v>
@@ -24231,25 +24231,25 @@
         <v>1.45</v>
       </c>
       <c r="AN109" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO109" t="n">
         <v>2</v>
       </c>
-      <c r="AO109" t="n">
-        <v>0.8</v>
-      </c>
       <c r="AP109" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AU109" t="n">
         <v>9</v>
@@ -24449,25 +24449,25 @@
         <v>1.83</v>
       </c>
       <c r="AN110" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AO110" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AU110" t="n">
         <v>5</v>
@@ -24667,25 +24667,25 @@
         <v>1.18</v>
       </c>
       <c r="AN111" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AO111" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AU111" t="n">
         <v>1</v>
@@ -24885,25 +24885,25 @@
         <v>1.47</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="AO112" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="AU112" t="n">
         <v>5</v>
@@ -25103,25 +25103,25 @@
         <v>2.15</v>
       </c>
       <c r="AN113" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="AO113" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP113" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AS113" t="n">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="AT113" t="n">
-        <v>2.07</v>
+        <v>2.46</v>
       </c>
       <c r="AU113" t="n">
         <v>-1</v>
@@ -25321,25 +25321,25 @@
         <v>1.78</v>
       </c>
       <c r="AN114" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="AO114" t="n">
-        <v>1</v>
+        <v>1.58</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AU114" t="n">
         <v>-1</v>
@@ -25539,25 +25539,25 @@
         <v>1.85</v>
       </c>
       <c r="AN115" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AO115" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AT115" t="n">
-        <v>3.11</v>
+        <v>2.82</v>
       </c>
       <c r="AU115" t="n">
         <v>-1</v>
@@ -25757,25 +25757,25 @@
         <v>2.15</v>
       </c>
       <c r="AN116" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AO116" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AU116" t="n">
         <v>8</v>
@@ -25975,25 +25975,25 @@
         <v>1.72</v>
       </c>
       <c r="AN117" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AO117" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="AS117" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AU117" t="n">
         <v>7</v>
@@ -26193,25 +26193,25 @@
         <v>1.3</v>
       </c>
       <c r="AN118" t="n">
-        <v>1.17</v>
+        <v>0.58</v>
       </c>
       <c r="AO118" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="AU118" t="n">
         <v>0</v>
@@ -26411,25 +26411,25 @@
         <v>1.47</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.83</v>
+        <v>1.62</v>
       </c>
       <c r="AO119" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AP119" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ119" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ119" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AR119" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AT119" t="n">
-        <v>3.13</v>
+        <v>2.69</v>
       </c>
       <c r="AU119" t="n">
         <v>2</v>
@@ -26629,25 +26629,25 @@
         <v>1.7</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AT120" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="AU120" t="n">
         <v>5</v>
@@ -26847,25 +26847,25 @@
         <v>2</v>
       </c>
       <c r="AN121" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AO121" t="n">
-        <v>0.67</v>
+        <v>1.69</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AU121" t="n">
         <v>3</v>
@@ -27065,25 +27065,25 @@
         <v>1.55</v>
       </c>
       <c r="AN122" t="n">
-        <v>2.17</v>
+        <v>1.69</v>
       </c>
       <c r="AO122" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AU122" t="n">
         <v>2</v>
@@ -27283,25 +27283,25 @@
         <v>2.35</v>
       </c>
       <c r="AN123" t="n">
-        <v>1.67</v>
+        <v>0.92</v>
       </c>
       <c r="AO123" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="AS123" t="n">
-        <v>0.92</v>
+        <v>1.01</v>
       </c>
       <c r="AT123" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AU123" t="n">
         <v>1</v>
@@ -27501,22 +27501,22 @@
         <v>2</v>
       </c>
       <c r="AN124" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AO124" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AT124" t="n">
         <v>2.58</v>
@@ -27719,25 +27719,25 @@
         <v>1.52</v>
       </c>
       <c r="AN125" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AO125" t="n">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AU125" t="n">
         <v>4</v>
@@ -27937,25 +27937,25 @@
         <v>1.45</v>
       </c>
       <c r="AN126" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AO126" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AU126" t="n">
         <v>4</v>
@@ -28155,25 +28155,25 @@
         <v>1.57</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AO127" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP127" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AU127" t="n">
         <v>3</v>
@@ -28373,22 +28373,22 @@
         <v>1.66</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AO128" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AT128" t="n">
         <v>2.62</v>
@@ -28591,25 +28591,25 @@
         <v>1.95</v>
       </c>
       <c r="AN129" t="n">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AO129" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="AU129" t="n">
         <v>4</v>
@@ -28809,25 +28809,25 @@
         <v>1.53</v>
       </c>
       <c r="AN130" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AO130" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AU130" t="n">
         <v>5</v>
@@ -29027,25 +29027,25 @@
         <v>1.38</v>
       </c>
       <c r="AN131" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AO131" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AU131" t="n">
         <v>6</v>
@@ -29245,25 +29245,25 @@
         <v>2.35</v>
       </c>
       <c r="AN132" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="AO132" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AS132" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AU132" t="n">
         <v>10</v>
@@ -29466,22 +29466,22 @@
         <v>0.86</v>
       </c>
       <c r="AO133" t="n">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="AU133" t="n">
         <v>4</v>
@@ -29681,25 +29681,25 @@
         <v>1.83</v>
       </c>
       <c r="AN134" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AO134" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AT134" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AU134" t="n">
         <v>7</v>
@@ -29899,25 +29899,25 @@
         <v>2</v>
       </c>
       <c r="AN135" t="n">
-        <v>0.86</v>
+        <v>1.57</v>
       </c>
       <c r="AO135" t="n">
-        <v>0.29</v>
+        <v>0.93</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AS135" t="n">
-        <v>0.99</v>
+        <v>1.1</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AU135" t="n">
         <v>7</v>
@@ -30117,25 +30117,25 @@
         <v>1.06</v>
       </c>
       <c r="AN136" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AO136" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AP136" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AU136" t="n">
         <v>2</v>
@@ -30335,25 +30335,25 @@
         <v>2.9</v>
       </c>
       <c r="AN137" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AO137" t="n">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AS137" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="AU137" t="n">
         <v>8</v>
@@ -30553,25 +30553,25 @@
         <v>2.2</v>
       </c>
       <c r="AN138" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO138" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AP138" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="AU138" t="n">
         <v>4</v>
@@ -30771,25 +30771,25 @@
         <v>1.47</v>
       </c>
       <c r="AN139" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AO139" t="n">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AU139" t="n">
         <v>10</v>
@@ -30989,25 +30989,25 @@
         <v>1.47</v>
       </c>
       <c r="AN140" t="n">
-        <v>0.71</v>
+        <v>1.6</v>
       </c>
       <c r="AO140" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AP140" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR140" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ140" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR140" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AS140" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AU140" t="n">
         <v>4</v>
@@ -31207,25 +31207,25 @@
         <v>1.2</v>
       </c>
       <c r="AN141" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="AO141" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AP141" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AU141" t="n">
         <v>4</v>
@@ -31425,25 +31425,25 @@
         <v>1.85</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AO142" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="AU142" t="n">
         <v>12</v>
@@ -31643,25 +31643,25 @@
         <v>2.2</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AO143" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AT143" t="n">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="AU143" t="n">
         <v>5</v>
@@ -31861,25 +31861,25 @@
         <v>1.42</v>
       </c>
       <c r="AN144" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AO144" t="n">
-        <v>0.71</v>
+        <v>1.73</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="AU144" t="n">
         <v>2</v>
@@ -32079,25 +32079,25 @@
         <v>1.42</v>
       </c>
       <c r="AN145" t="n">
-        <v>1.57</v>
+        <v>0.87</v>
       </c>
       <c r="AO145" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AU145" t="n">
         <v>2</v>
@@ -32297,25 +32297,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO146" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AU146" t="n">
         <v>5</v>
@@ -32515,25 +32515,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AO147" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AU147" t="n">
         <v>6</v>
@@ -32733,25 +32733,25 @@
         <v>2.35</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AO148" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="AU148" t="n">
         <v>9</v>
@@ -32951,25 +32951,25 @@
         <v>1.66</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.75</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO149" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AQ149" t="n">
         <v>0.88</v>
       </c>
-      <c r="AP149" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ149" t="n">
-        <v>0.76</v>
-      </c>
       <c r="AR149" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS149" t="n">
         <v>1.07</v>
       </c>
-      <c r="AS149" t="n">
-        <v>0.82</v>
-      </c>
       <c r="AT149" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="AU149" t="n">
         <v>1</v>
@@ -33169,25 +33169,25 @@
         <v>1.72</v>
       </c>
       <c r="AN150" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO150" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR150" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS150" t="n">
         <v>1.28</v>
       </c>
-      <c r="AS150" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AT150" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AU150" t="n">
         <v>10</v>
@@ -33387,25 +33387,25 @@
         <v>1.95</v>
       </c>
       <c r="AN151" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AO151" t="n">
-        <v>0.25</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ151" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="AU151" t="n">
         <v>5</v>
@@ -33605,25 +33605,25 @@
         <v>1.17</v>
       </c>
       <c r="AN152" t="n">
-        <v>0.88</v>
+        <v>0.5</v>
       </c>
       <c r="AO152" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ152" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.73</v>
+        <v>2.57</v>
       </c>
       <c r="AU152" t="n">
         <v>5</v>
@@ -33823,25 +33823,25 @@
         <v>1.7</v>
       </c>
       <c r="AN153" t="n">
-        <v>2.63</v>
+        <v>1.63</v>
       </c>
       <c r="AO153" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AT153" t="n">
-        <v>3.02</v>
+        <v>2.67</v>
       </c>
       <c r="AU153" t="n">
         <v>1</v>
@@ -34041,25 +34041,25 @@
         <v>1.2</v>
       </c>
       <c r="AN154" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AO154" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ154" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AT154" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="AU154" t="n">
         <v>4</v>
@@ -34259,25 +34259,25 @@
         <v>1.57</v>
       </c>
       <c r="AN155" t="n">
-        <v>1</v>
+        <v>1.53</v>
       </c>
       <c r="AO155" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AP155" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS155" t="n">
         <v>1.53</v>
       </c>
-      <c r="AQ155" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AT155" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AU155" t="n">
         <v>6</v>
@@ -34477,25 +34477,25 @@
         <v>1.23</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="AO156" t="n">
-        <v>0.63</v>
+        <v>1.59</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AU156" t="n">
         <v>1</v>
@@ -34695,25 +34695,25 @@
         <v>1.83</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO157" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AS157" t="n">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AU157" t="n">
         <v>9</v>
@@ -34913,25 +34913,25 @@
         <v>1.37</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.38</v>
+        <v>0.76</v>
       </c>
       <c r="AO158" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AU158" t="n">
         <v>1</v>
@@ -35131,25 +35131,25 @@
         <v>1.53</v>
       </c>
       <c r="AN159" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO159" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="AU159" t="n">
         <v>4</v>
@@ -35349,25 +35349,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AO160" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AT160" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="AU160" t="n">
         <v>5</v>
@@ -35567,25 +35567,25 @@
         <v>1.7</v>
       </c>
       <c r="AN161" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AO161" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU161" t="n">
         <v>7</v>
@@ -35785,25 +35785,25 @@
         <v>1.63</v>
       </c>
       <c r="AN162" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AO162" t="n">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="AU162" t="n">
         <v>4</v>
@@ -36003,25 +36003,25 @@
         <v>1.6</v>
       </c>
       <c r="AN163" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AO163" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AP163" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ163" t="n">
         <v>1.53</v>
       </c>
-      <c r="AQ163" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AR163" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="AU163" t="n">
         <v>7</v>
@@ -36221,25 +36221,25 @@
         <v>2.15</v>
       </c>
       <c r="AN164" t="n">
-        <v>0.75</v>
+        <v>1.72</v>
       </c>
       <c r="AO164" t="n">
-        <v>0.22</v>
+        <v>0.78</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ164" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AS164" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AU164" t="n">
         <v>5</v>
@@ -36439,25 +36439,25 @@
         <v>1.55</v>
       </c>
       <c r="AN165" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AO165" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ165" t="n">
         <v>1.56</v>
       </c>
-      <c r="AP165" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ165" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AR165" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="AU165" t="n">
         <v>4</v>
@@ -36657,25 +36657,25 @@
         <v>2.15</v>
       </c>
       <c r="AN166" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO166" t="n">
         <v>1.56</v>
       </c>
-      <c r="AO166" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AP166" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AT166" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AU166" t="n">
         <v>5</v>
@@ -36875,25 +36875,25 @@
         <v>1.58</v>
       </c>
       <c r="AN167" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AO167" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AU167" t="n">
         <v>4</v>
@@ -37093,25 +37093,25 @@
         <v>1.73</v>
       </c>
       <c r="AN168" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO168" t="n">
-        <v>0.89</v>
+        <v>1.39</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AU168" t="n">
         <v>5</v>
@@ -37311,25 +37311,25 @@
         <v>1.46</v>
       </c>
       <c r="AN169" t="n">
-        <v>0.88</v>
+        <v>1.39</v>
       </c>
       <c r="AO169" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AP169" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AU169" t="n">
         <v>5</v>
@@ -37529,25 +37529,25 @@
         <v>1.83</v>
       </c>
       <c r="AN170" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AO170" t="n">
-        <v>0.13</v>
+        <v>0.61</v>
       </c>
       <c r="AP170" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AU170" t="n">
         <v>7</v>
@@ -37747,25 +37747,25 @@
         <v>1.68</v>
       </c>
       <c r="AN171" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AO171" t="n">
         <v>1.56</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="AU171" t="n">
         <v>4</v>
@@ -37965,25 +37965,25 @@
         <v>2.2</v>
       </c>
       <c r="AN172" t="n">
-        <v>2.44</v>
+        <v>1.67</v>
       </c>
       <c r="AO172" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT172" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="AU172" t="n">
         <v>6</v>
@@ -38183,25 +38183,25 @@
         <v>1.63</v>
       </c>
       <c r="AN173" t="n">
-        <v>1.89</v>
+        <v>1.32</v>
       </c>
       <c r="AO173" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ173" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AT173" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="AU173" t="n">
         <v>6</v>
@@ -38401,25 +38401,25 @@
         <v>1.69</v>
       </c>
       <c r="AN174" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AO174" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ174" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS174" t="n">
         <v>1.24</v>
       </c>
-      <c r="AR174" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AS174" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AT174" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AU174" t="n">
         <v>6</v>
@@ -38619,25 +38619,25 @@
         <v>1.24</v>
       </c>
       <c r="AN175" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="AO175" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AU175" t="n">
         <v>2</v>
@@ -38837,25 +38837,25 @@
         <v>1.2</v>
       </c>
       <c r="AN176" t="n">
-        <v>1.33</v>
+        <v>0.79</v>
       </c>
       <c r="AO176" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="AU176" t="n">
         <v>4</v>
@@ -39055,25 +39055,25 @@
         <v>2.1</v>
       </c>
       <c r="AN177" t="n">
-        <v>1</v>
+        <v>1.58</v>
       </c>
       <c r="AO177" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AS177" t="n">
-        <v>0.98</v>
+        <v>1.18</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AU177" t="n">
         <v>3</v>
@@ -39273,22 +39273,22 @@
         <v>1.58</v>
       </c>
       <c r="AN178" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AO178" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AT178" t="n">
         <v>2.77</v>
@@ -39491,25 +39491,25 @@
         <v>2.1</v>
       </c>
       <c r="AN179" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AO179" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AU179" t="n">
         <v>7</v>
@@ -39709,25 +39709,25 @@
         <v>1.87</v>
       </c>
       <c r="AN180" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AO180" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="AU180" t="n">
         <v>4</v>
@@ -39927,25 +39927,25 @@
         <v>1.88</v>
       </c>
       <c r="AN181" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AO181" t="n">
-        <v>0.89</v>
+        <v>1.63</v>
       </c>
       <c r="AP181" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR181" t="n">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="AS181" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="AU181" t="n">
         <v>3</v>
@@ -40148,22 +40148,22 @@
         <v>1</v>
       </c>
       <c r="AO182" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AU182" t="n">
         <v>3</v>
@@ -40363,22 +40363,22 @@
         <v>1.93</v>
       </c>
       <c r="AN183" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AO183" t="n">
-        <v>0.11</v>
+        <v>0.7</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AS183" t="n">
-        <v>0.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT183" t="n">
         <v>2.24</v>
@@ -40581,25 +40581,25 @@
         <v>1.68</v>
       </c>
       <c r="AN184" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AO184" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR184" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AT184" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AU184" t="n">
         <v>2</v>
@@ -40799,25 +40799,25 @@
         <v>1.68</v>
       </c>
       <c r="AN185" t="n">
-        <v>0.78</v>
+        <v>1.75</v>
       </c>
       <c r="AO185" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AT185" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AU185" t="n">
         <v>8</v>
@@ -41017,25 +41017,25 @@
         <v>1.41</v>
       </c>
       <c r="AN186" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="AO186" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AP186" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AT186" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="AU186" t="n">
         <v>3</v>
@@ -41235,25 +41235,25 @@
         <v>1.95</v>
       </c>
       <c r="AN187" t="n">
-        <v>0.78</v>
+        <v>1.25</v>
       </c>
       <c r="AO187" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AP187" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AT187" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AU187" t="n">
         <v>5</v>
@@ -41453,25 +41453,25 @@
         <v>2</v>
       </c>
       <c r="AN188" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AO188" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS188" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AT188" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AU188" t="n">
         <v>3</v>
@@ -41671,25 +41671,25 @@
         <v>1.95</v>
       </c>
       <c r="AN189" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AO189" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ189" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AS189" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AU189" t="n">
         <v>4</v>
@@ -41889,25 +41889,25 @@
         <v>1.72</v>
       </c>
       <c r="AN190" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AO190" t="n">
-        <v>2.22</v>
+        <v>1.65</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AT190" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="AU190" t="n">
         <v>2</v>
@@ -42107,25 +42107,25 @@
         <v>1.42</v>
       </c>
       <c r="AN191" t="n">
-        <v>0.7</v>
+        <v>1.67</v>
       </c>
       <c r="AO191" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AT191" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AU191" t="n">
         <v>7</v>
@@ -42325,25 +42325,25 @@
         <v>2.05</v>
       </c>
       <c r="AN192" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AR192" t="n">
         <v>1.4</v>
       </c>
-      <c r="AO192" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP192" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AQ192" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR192" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AS192" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.71</v>
+        <v>2.52</v>
       </c>
       <c r="AU192" t="n">
         <v>6</v>
@@ -42543,25 +42543,25 @@
         <v>2</v>
       </c>
       <c r="AN193" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AO193" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ193" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="AU193" t="n">
         <v>4</v>
@@ -42761,25 +42761,25 @@
         <v>1.46</v>
       </c>
       <c r="AN194" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AO194" t="n">
-        <v>0.9</v>
+        <v>1.57</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AU194" t="n">
         <v>5</v>
@@ -42979,25 +42979,25 @@
         <v>1.43</v>
       </c>
       <c r="AN195" t="n">
-        <v>1.2</v>
+        <v>0.86</v>
       </c>
       <c r="AO195" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ195" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AS195" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AU195" t="n">
         <v>9</v>
@@ -43197,25 +43197,25 @@
         <v>1.63</v>
       </c>
       <c r="AN196" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AO196" t="n">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AU196" t="n">
         <v>3</v>
@@ -43415,25 +43415,25 @@
         <v>1.17</v>
       </c>
       <c r="AN197" t="n">
-        <v>1.18</v>
+        <v>0.67</v>
       </c>
       <c r="AO197" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AU197" t="n">
         <v>5</v>
@@ -43633,25 +43633,25 @@
         <v>1.73</v>
       </c>
       <c r="AN198" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AO198" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS198" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="AU198" t="n">
         <v>3</v>
@@ -43851,25 +43851,25 @@
         <v>1.9</v>
       </c>
       <c r="AN199" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AO199" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AU199" t="n">
         <v>6</v>
@@ -44069,25 +44069,25 @@
         <v>2.1</v>
       </c>
       <c r="AN200" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AO200" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="AU200" t="n">
         <v>8</v>
@@ -44287,25 +44287,25 @@
         <v>1.71</v>
       </c>
       <c r="AN201" t="n">
-        <v>0.7</v>
+        <v>1.14</v>
       </c>
       <c r="AO201" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP201" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="AU201" t="n">
         <v>3</v>
@@ -44505,25 +44505,25 @@
         <v>1.42</v>
       </c>
       <c r="AN202" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AO202" t="n">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="AU202" t="n">
         <v>4</v>
@@ -44723,25 +44723,25 @@
         <v>1.38</v>
       </c>
       <c r="AN203" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="AO203" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AP203" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AU203" t="n">
         <v>3</v>
@@ -44944,22 +44944,22 @@
         <v>0.91</v>
       </c>
       <c r="AO204" t="n">
-        <v>0.1</v>
+        <v>0.68</v>
       </c>
       <c r="AP204" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AR204" t="n">
         <v>1.12</v>
       </c>
-      <c r="AQ204" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AR204" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AS204" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AU204" t="n">
         <v>5</v>
@@ -45159,25 +45159,25 @@
         <v>1.65</v>
       </c>
       <c r="AN205" t="n">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="AO205" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AU205" t="n">
         <v>1</v>
@@ -45380,22 +45380,22 @@
         <v>1.82</v>
       </c>
       <c r="AO206" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AT206" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AU206" t="n">
         <v>4</v>
@@ -45595,25 +45595,25 @@
         <v>1.53</v>
       </c>
       <c r="AN207" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AO207" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="AU207" t="n">
         <v>3</v>
@@ -45813,25 +45813,25 @@
         <v>1.68</v>
       </c>
       <c r="AN208" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AO208" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ208" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AU208" t="n">
         <v>7</v>
@@ -46031,25 +46031,25 @@
         <v>1.98</v>
       </c>
       <c r="AN209" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AO209" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ209" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR209" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AS209" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AT209" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AU209" t="n">
         <v>4</v>
@@ -46249,25 +46249,25 @@
         <v>1.98</v>
       </c>
       <c r="AN210" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AO210" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AU210" t="n">
         <v>6</v>
@@ -46467,25 +46467,25 @@
         <v>1.53</v>
       </c>
       <c r="AN211" t="n">
-        <v>1.36</v>
+        <v>0.91</v>
       </c>
       <c r="AO211" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AU211" t="n">
         <v>3</v>
@@ -46685,25 +46685,25 @@
         <v>2.15</v>
       </c>
       <c r="AN212" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AO212" t="n">
-        <v>0.09</v>
+        <v>0.65</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AU212" t="n">
         <v>13</v>
@@ -46903,25 +46903,25 @@
         <v>1.46</v>
       </c>
       <c r="AN213" t="n">
-        <v>2.09</v>
+        <v>1.52</v>
       </c>
       <c r="AO213" t="n">
-        <v>0.91</v>
+        <v>1.52</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AU213" t="n">
         <v>2</v>
@@ -47121,25 +47121,25 @@
         <v>1.36</v>
       </c>
       <c r="AN214" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AS214" t="n">
         <v>1.55</v>
       </c>
-      <c r="AO214" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AP214" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AQ214" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AR214" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS214" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AT214" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AU214" t="n">
         <v>2</v>
@@ -47339,25 +47339,25 @@
         <v>1.82</v>
       </c>
       <c r="AN215" t="n">
-        <v>0.91</v>
+        <v>1.65</v>
       </c>
       <c r="AO215" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ215" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AT215" t="n">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="AU215" t="n">
         <v>10</v>
@@ -47557,25 +47557,25 @@
         <v>1.55</v>
       </c>
       <c r="AN216" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AO216" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AT216" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="AU216" t="n">
         <v>5</v>
@@ -47775,25 +47775,25 @@
         <v>1.5</v>
       </c>
       <c r="AN217" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AO217" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AP217" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ217" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR217" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS217" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="AU217" t="n">
         <v>5</v>
@@ -47993,25 +47993,25 @@
         <v>1.85</v>
       </c>
       <c r="AN218" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO218" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP218" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ218" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR218" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="AU218" t="n">
         <v>12</v>
@@ -48211,25 +48211,25 @@
         <v>1.53</v>
       </c>
       <c r="AN219" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AO219" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="AU219" t="n">
         <v>1</v>
@@ -48429,25 +48429,25 @@
         <v>1.4</v>
       </c>
       <c r="AN220" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AO220" t="n">
-        <v>2.33</v>
+        <v>1.71</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AU220" t="n">
         <v>2</v>
@@ -48647,25 +48647,25 @@
         <v>1.73</v>
       </c>
       <c r="AN221" t="n">
-        <v>0.73</v>
+        <v>1.08</v>
       </c>
       <c r="AO221" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AP221" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR221" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AS221" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AT221" t="n">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="AU221" t="n">
         <v>5</v>
@@ -48865,25 +48865,25 @@
         <v>1.26</v>
       </c>
       <c r="AN222" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="AO222" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AP222" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR222" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AS222" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AT222" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AU222" t="n">
         <v>1</v>
@@ -49083,25 +49083,25 @@
         <v>2.05</v>
       </c>
       <c r="AN223" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO223" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AU223" t="n">
         <v>9</v>
@@ -49301,22 +49301,22 @@
         <v>2.3</v>
       </c>
       <c r="AN224" t="n">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="AO224" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ224" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AT224" t="n">
         <v>2.54</v>
@@ -49519,25 +49519,25 @@
         <v>1.49</v>
       </c>
       <c r="AN225" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AO225" t="n">
-        <v>1</v>
+        <v>1.46</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR225" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AU225" t="n">
         <v>4</v>
@@ -49737,25 +49737,25 @@
         <v>1.2</v>
       </c>
       <c r="AN226" t="n">
-        <v>1.17</v>
+        <v>0.63</v>
       </c>
       <c r="AO226" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AS226" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AU226" t="n">
         <v>0</v>
@@ -49955,25 +49955,25 @@
         <v>1.51</v>
       </c>
       <c r="AN227" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AO227" t="n">
-        <v>1.08</v>
+        <v>1.56</v>
       </c>
       <c r="AP227" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ227" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR227" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AS227" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AT227" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="AU227" t="n">
         <v>4</v>
@@ -50173,25 +50173,25 @@
         <v>1.5</v>
       </c>
       <c r="AN228" t="n">
-        <v>1.08</v>
+        <v>1.68</v>
       </c>
       <c r="AO228" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS228" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AT228" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="AU228" t="n">
         <v>10</v>
@@ -50391,25 +50391,25 @@
         <v>2.18</v>
       </c>
       <c r="AN229" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AO229" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AP229" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AU229" t="n">
         <v>4</v>
@@ -50609,25 +50609,25 @@
         <v>2.02</v>
       </c>
       <c r="AN230" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AO230" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ230" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR230" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AS230" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AU230" t="n">
         <v>8</v>
@@ -50827,25 +50827,25 @@
         <v>2.32</v>
       </c>
       <c r="AN231" t="n">
-        <v>1.23</v>
+        <v>1.52</v>
       </c>
       <c r="AO231" t="n">
-        <v>0.08</v>
+        <v>0.64</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR231" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AT231" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AU231" t="n">
         <v>9</v>
@@ -51045,25 +51045,25 @@
         <v>1.82</v>
       </c>
       <c r="AN232" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AO232" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ232" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR232" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS232" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AT232" t="n">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="AU232" t="n">
         <v>5</v>
@@ -51263,25 +51263,25 @@
         <v>1.72</v>
       </c>
       <c r="AN233" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AO233" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AP233" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ233" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS233" t="n">
         <v>1.25</v>
       </c>
-      <c r="AP233" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AQ233" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="AR233" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AS233" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AT233" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AU233" t="n">
         <v>3</v>
@@ -51481,25 +51481,25 @@
         <v>1.72</v>
       </c>
       <c r="AN234" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AO234" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ234" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR234" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AS234" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AU234" t="n">
         <v>5</v>
@@ -51699,25 +51699,25 @@
         <v>1.36</v>
       </c>
       <c r="AN235" t="n">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AO235" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AP235" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ235" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR235" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AS235" t="n">
         <v>1.38</v>
       </c>
-      <c r="AP235" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ235" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR235" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AS235" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AT235" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="AU235" t="n">
         <v>4</v>
@@ -51917,25 +51917,25 @@
         <v>2.05</v>
       </c>
       <c r="AN236" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AO236" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR236" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AS236" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AT236" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="AU236" t="n">
         <v>2</v>
@@ -52135,25 +52135,25 @@
         <v>1.44</v>
       </c>
       <c r="AN237" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AO237" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AP237" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ237" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR237" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AT237" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="AU237" t="n">
         <v>4</v>
@@ -52353,25 +52353,25 @@
         <v>1.58</v>
       </c>
       <c r="AN238" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AO238" t="n">
-        <v>2.23</v>
+        <v>1.62</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR238" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AS238" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AU238" t="n">
         <v>2</v>
@@ -52571,25 +52571,25 @@
         <v>1.58</v>
       </c>
       <c r="AN239" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AO239" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR239" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AS239" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AT239" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AU239" t="n">
         <v>8</v>
@@ -52789,25 +52789,25 @@
         <v>2</v>
       </c>
       <c r="AN240" t="n">
-        <v>0.67</v>
+        <v>1.12</v>
       </c>
       <c r="AO240" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AP240" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR240" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AS240" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AT240" t="n">
-        <v>2.51</v>
+        <v>2.73</v>
       </c>
       <c r="AU240" t="n">
         <v>4</v>
@@ -53007,25 +53007,25 @@
         <v>1.62</v>
       </c>
       <c r="AN241" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AO241" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ241" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR241" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AS241" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AT241" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AU241" t="n">
         <v>7</v>
@@ -53225,25 +53225,25 @@
         <v>1.52</v>
       </c>
       <c r="AN242" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AO242" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR242" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AS242" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AT242" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AU242" t="n">
         <v>7</v>
@@ -53446,22 +53446,22 @@
         <v>1</v>
       </c>
       <c r="AO243" t="n">
-        <v>0.54</v>
+        <v>0.88</v>
       </c>
       <c r="AP243" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ243" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR243" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="AU243" t="n">
         <v>3</v>
@@ -53661,25 +53661,25 @@
         <v>1.32</v>
       </c>
       <c r="AN244" t="n">
-        <v>1.15</v>
+        <v>0.62</v>
       </c>
       <c r="AO244" t="n">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="AP244" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR244" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AS244" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AT244" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AU244" t="n">
         <v>4</v>
@@ -53879,25 +53879,25 @@
         <v>1.46</v>
       </c>
       <c r="AN245" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AO245" t="n">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR245" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AS245" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AT245" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AU245" t="n">
         <v>4</v>
@@ -54097,25 +54097,25 @@
         <v>1.29</v>
       </c>
       <c r="AN246" t="n">
-        <v>1.23</v>
+        <v>0.89</v>
       </c>
       <c r="AO246" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR246" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AS246" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AT246" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="AU246" t="n">
         <v>5</v>
@@ -54315,25 +54315,25 @@
         <v>2.17</v>
       </c>
       <c r="AN247" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AO247" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ247" t="n">
         <v>1.15</v>
       </c>
-      <c r="AP247" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AQ247" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="AR247" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AS247" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AT247" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="AU247" t="n">
         <v>4</v>
@@ -54533,25 +54533,25 @@
         <v>1.92</v>
       </c>
       <c r="AN248" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AO248" t="n">
         <v>1</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR248" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AS248" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AT248" t="n">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="AU248" t="n">
         <v>4</v>
@@ -54751,25 +54751,25 @@
         <v>1.26</v>
       </c>
       <c r="AN249" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AO249" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR249" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AS249" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AT249" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AU249" t="n">
         <v>4</v>
@@ -54972,22 +54972,22 @@
         <v>1.85</v>
       </c>
       <c r="AO250" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS250" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AT250" t="n">
-        <v>3.13</v>
+        <v>2.98</v>
       </c>
       <c r="AU250" t="n">
         <v>4</v>
@@ -55187,25 +55187,25 @@
         <v>1.82</v>
       </c>
       <c r="AN251" t="n">
-        <v>1</v>
+        <v>1.59</v>
       </c>
       <c r="AO251" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR251" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AS251" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AT251" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="AU251" t="n">
         <v>4</v>
@@ -55405,25 +55405,25 @@
         <v>1.85</v>
       </c>
       <c r="AN252" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AO252" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ252" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR252" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AS252" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AT252" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AU252" t="n">
         <v>5</v>
@@ -55623,25 +55623,25 @@
         <v>2.6</v>
       </c>
       <c r="AN253" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AO253" t="n">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ253" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR253" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AS253" t="n">
         <v>1.11</v>
       </c>
       <c r="AT253" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="AU253" t="n">
         <v>7</v>
@@ -55841,25 +55841,25 @@
         <v>2.85</v>
       </c>
       <c r="AN254" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.57</v>
+        <v>0.96</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ254" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR254" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AS254" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AT254" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AU254" t="n">
         <v>5</v>
@@ -56059,25 +56059,25 @@
         <v>1.34</v>
       </c>
       <c r="AN255" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AO255" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR255" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AS255" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AT255" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AU255" t="n">
         <v>8</v>
@@ -56277,25 +56277,25 @@
         <v>1.61</v>
       </c>
       <c r="AN256" t="n">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AO256" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AP256" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ256" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR256" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AS256" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AT256" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AU256" t="n">
         <v>3</v>
@@ -56495,22 +56495,22 @@
         <v>1.73</v>
       </c>
       <c r="AN257" t="n">
-        <v>0.85</v>
+        <v>1.25</v>
       </c>
       <c r="AO257" t="n">
-        <v>0.86</v>
+        <v>1.21</v>
       </c>
       <c r="AP257" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ257" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR257" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AS257" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AT257" t="n">
         <v>2.95</v>
@@ -56713,25 +56713,25 @@
         <v>1.3</v>
       </c>
       <c r="AN258" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="AO258" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AP258" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR258" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AS258" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AT258" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="AU258" t="n">
         <v>4</v>
@@ -56931,25 +56931,25 @@
         <v>1.72</v>
       </c>
       <c r="AN259" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="AO259" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="AP259" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ259" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR259" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AS259" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="AU259" t="n">
         <v>11</v>
@@ -57149,25 +57149,25 @@
         <v>2</v>
       </c>
       <c r="AN260" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AO260" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AP260" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ260" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR260" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AS260" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AT260" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AU260" t="n">
         <v>7</v>
@@ -57367,25 +57367,25 @@
         <v>1.58</v>
       </c>
       <c r="AN261" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="AO261" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR261" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AS261" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AT261" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AU261" t="n">
         <v>5</v>
@@ -57585,25 +57585,25 @@
         <v>1.25</v>
       </c>
       <c r="AN262" t="n">
-        <v>1.29</v>
+        <v>0.68</v>
       </c>
       <c r="AO262" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AP262" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ262" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR262" t="n">
         <v>1.11</v>
       </c>
       <c r="AS262" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="AT262" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AU262" t="n">
         <v>6</v>
@@ -57803,25 +57803,25 @@
         <v>0</v>
       </c>
       <c r="AN263" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AO263" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="AP263" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR263" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="AT263" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AU263" t="n">
         <v>5</v>
@@ -58021,25 +58021,25 @@
         <v>0</v>
       </c>
       <c r="AN264" t="n">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="AO264" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AP264" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ264" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR264" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS264" t="n">
         <v>1.53</v>
       </c>
-      <c r="AQ264" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR264" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS264" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AT264" t="n">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="AU264" t="n">
         <v>2</v>
@@ -58239,25 +58239,25 @@
         <v>0</v>
       </c>
       <c r="AN265" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AO265" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ265" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR265" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AS265" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AT265" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AU265" t="n">
         <v>5</v>
@@ -58457,25 +58457,25 @@
         <v>1.4</v>
       </c>
       <c r="AN266" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AO266" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ266" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR266" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AS266" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AT266" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="AU266" t="n">
         <v>3</v>
@@ -58675,25 +58675,25 @@
         <v>1.33</v>
       </c>
       <c r="AN267" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="AO267" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AP267" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR267" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AS267" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AT267" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AU267" t="n">
         <v>3</v>
@@ -58893,25 +58893,25 @@
         <v>2.88</v>
       </c>
       <c r="AN268" t="n">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="AP268" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR268" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AS268" t="n">
         <v>1.12</v>
       </c>
       <c r="AT268" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="AU268" t="n">
         <v>6</v>
@@ -59111,25 +59111,25 @@
         <v>1.67</v>
       </c>
       <c r="AN269" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AO269" t="n">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ269" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR269" t="n">
         <v>1.5</v>
       </c>
       <c r="AS269" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AT269" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="AU269" t="n">
         <v>7</v>
@@ -59329,25 +59329,25 @@
         <v>2.25</v>
       </c>
       <c r="AN270" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="AP270" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR270" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AS270" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT270" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AU270" t="n">
         <v>8</v>
@@ -59547,25 +59547,25 @@
         <v>1.62</v>
       </c>
       <c r="AN271" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AO271" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AP271" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ271" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR271" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AS271" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AT271" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="AU271" t="n">
         <v>4</v>
@@ -59765,25 +59765,25 @@
         <v>0</v>
       </c>
       <c r="AN272" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.67</v>
+        <v>0.87</v>
       </c>
       <c r="AP272" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ272" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR272" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AS272" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AT272" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AU272" t="n">
         <v>3</v>
@@ -59983,25 +59983,25 @@
         <v>0</v>
       </c>
       <c r="AN273" t="n">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
       <c r="AO273" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AP273" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR273" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AS273" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AT273" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="AU273" t="n">
         <v>5</v>
@@ -60201,25 +60201,25 @@
         <v>0</v>
       </c>
       <c r="AN274" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AO274" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ274" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR274" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS274" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AT274" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AU274" t="n">
         <v>2</v>
@@ -60419,22 +60419,22 @@
         <v>0</v>
       </c>
       <c r="AN275" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AO275" t="n">
-        <v>0.87</v>
+        <v>1.27</v>
       </c>
       <c r="AP275" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ275" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR275" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AS275" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AT275" t="n">
         <v>2.71</v>
@@ -60637,25 +60637,25 @@
         <v>0</v>
       </c>
       <c r="AN276" t="n">
-        <v>1.4</v>
+        <v>0.73</v>
       </c>
       <c r="AO276" t="n">
-        <v>0.73</v>
+        <v>1.1</v>
       </c>
       <c r="AP276" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ276" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR276" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS276" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AT276" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AU276" t="n">
         <v>3</v>
@@ -60855,25 +60855,25 @@
         <v>0</v>
       </c>
       <c r="AN277" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO277" t="n">
         <v>1.47</v>
       </c>
-      <c r="AO277" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AP277" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ277" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AR277" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AS277" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AT277" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AU277" t="n">
         <v>9</v>
@@ -61073,25 +61073,25 @@
         <v>0</v>
       </c>
       <c r="AN278" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AO278" t="n">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ278" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR278" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AS278" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AT278" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AU278" t="n">
         <v>5</v>
@@ -61291,25 +61291,25 @@
         <v>0</v>
       </c>
       <c r="AN279" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="AO279" t="n">
         <v>1.8</v>
       </c>
       <c r="AP279" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ279" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR279" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AS279" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AT279" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="AU279" t="n">
         <v>7</v>
@@ -61509,25 +61509,25 @@
         <v>0</v>
       </c>
       <c r="AN280" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AO280" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ280" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR280" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AS280" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AT280" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AU280" t="n">
         <v>11</v>
@@ -61727,25 +61727,25 @@
         <v>2.7</v>
       </c>
       <c r="AN281" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP281" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR281" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AS281" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT281" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="AU281" t="n">
         <v>4</v>
@@ -61945,25 +61945,25 @@
         <v>1.38</v>
       </c>
       <c r="AN282" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AO282" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AP282" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ282" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR282" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS282" t="n">
         <v>1.52</v>
       </c>
-      <c r="AS282" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AT282" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AU282" t="n">
         <v>3</v>
@@ -62163,22 +62163,22 @@
         <v>1.42</v>
       </c>
       <c r="AN283" t="n">
-        <v>1.07</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO283" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="AP283" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ283" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR283" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AS283" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AT283" t="n">
         <v>2.65</v>
@@ -62381,25 +62381,25 @@
         <v>1.42</v>
       </c>
       <c r="AN284" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AO284" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AP284" t="n">
-        <v>1.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ284" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR284" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AS284" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AT284" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="AU284" t="n">
         <v>5</v>
@@ -62599,25 +62599,25 @@
         <v>1.4</v>
       </c>
       <c r="AN285" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="AO285" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AP285" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ285" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR285" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AS285" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AT285" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="AU285" t="n">
         <v>3</v>
@@ -62817,25 +62817,25 @@
         <v>3.4</v>
       </c>
       <c r="AN286" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AP286" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ286" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR286" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AS286" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT286" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="AU286" t="n">
         <v>4</v>
@@ -63035,25 +63035,25 @@
         <v>1.57</v>
       </c>
       <c r="AN287" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="AO287" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AP287" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ287" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR287" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AS287" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AT287" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AU287" t="n">
         <v>7</v>
@@ -63253,25 +63253,25 @@
         <v>1.25</v>
       </c>
       <c r="AN288" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AO288" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AP288" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ288" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR288" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AS288" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AT288" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="AU288" t="n">
         <v>2</v>
@@ -63471,25 +63471,25 @@
         <v>2</v>
       </c>
       <c r="AN289" t="n">
-        <v>0.87</v>
+        <v>1.29</v>
       </c>
       <c r="AO289" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP289" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ289" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR289" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AS289" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AT289" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="AU289" t="n">
         <v>4</v>
@@ -63692,22 +63692,22 @@
         <v>1</v>
       </c>
       <c r="AO290" t="n">
-        <v>1.69</v>
+        <v>1.34</v>
       </c>
       <c r="AP290" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AQ290" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="AR290" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AS290" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AT290" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AU290" t="n">
         <v>3</v>
@@ -63907,25 +63907,25 @@
         <v>1.21</v>
       </c>
       <c r="AN291" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AO291" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AP291" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AQ291" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AR291" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS291" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AT291" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AU291" t="n">
         <v>1</v>
@@ -64125,25 +64125,25 @@
         <v>2</v>
       </c>
       <c r="AN292" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AO292" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AP292" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AQ292" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AR292" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AS292" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AT292" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="AU292" t="n">
         <v>8</v>
@@ -64343,25 +64343,25 @@
         <v>1.72</v>
       </c>
       <c r="AN293" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AO293" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="AP293" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AQ293" t="n">
-        <v>1.82</v>
+        <v>1.56</v>
       </c>
       <c r="AR293" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AS293" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AT293" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU293" t="n">
         <v>4</v>
@@ -64561,22 +64561,22 @@
         <v>2.3</v>
       </c>
       <c r="AN294" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AO294" t="n">
-        <v>0.75</v>
+        <v>1.09</v>
       </c>
       <c r="AP294" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AQ294" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="AR294" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AS294" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AT294" t="n">
         <v>2.58</v>
@@ -64782,22 +64782,22 @@
         <v>1.75</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="AP295" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ295" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AR295" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AS295" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AT295" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AU295" t="n">
         <v>10</v>
@@ -64997,25 +64997,25 @@
         <v>1.3</v>
       </c>
       <c r="AN296" t="n">
-        <v>1.38</v>
+        <v>0.75</v>
       </c>
       <c r="AO296" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AP296" t="n">
-        <v>1.35</v>
+        <v>0.74</v>
       </c>
       <c r="AQ296" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AR296" t="n">
         <v>1.12</v>
       </c>
       <c r="AS296" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AT296" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="AU296" t="n">
         <v>3</v>
@@ -65215,25 +65215,25 @@
         <v>1.82</v>
       </c>
       <c r="AN297" t="n">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="AO297" t="n">
-        <v>0.88</v>
+        <v>1.22</v>
       </c>
       <c r="AP297" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="AQ297" t="n">
-        <v>0.82</v>
+        <v>1.24</v>
       </c>
       <c r="AR297" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AS297" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AT297" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="AU297" t="n">
         <v>6</v>
@@ -65433,25 +65433,25 @@
         <v>1.78</v>
       </c>
       <c r="AN298" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AO298" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="AP298" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AQ298" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AR298" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AS298" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AT298" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AU298" t="n">
         <v>8</v>
@@ -65651,25 +65651,25 @@
         <v>2.1</v>
       </c>
       <c r="AN299" t="n">
-        <v>1.44</v>
+        <v>1.06</v>
       </c>
       <c r="AO299" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP299" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ299" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR299" t="n">
         <v>1.19</v>
       </c>
-      <c r="AP299" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ299" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR299" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AS299" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AT299" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AU299" t="n">
         <v>3</v>
@@ -65869,25 +65869,25 @@
         <v>2.4</v>
       </c>
       <c r="AN300" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AO300" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="AP300" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AQ300" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="AR300" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AS300" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AT300" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="AU300" t="n">
         <v>8</v>
@@ -66087,25 +66087,25 @@
         <v>2.8</v>
       </c>
       <c r="AN301" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.13</v>
+        <v>0.76</v>
       </c>
       <c r="AP301" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AQ301" t="n">
-        <v>0.12</v>
+        <v>0.74</v>
       </c>
       <c r="AR301" t="n">
         <v>1.52</v>
       </c>
       <c r="AS301" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AT301" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AU301" t="n">
         <v>5</v>
@@ -66305,25 +66305,25 @@
         <v>1.2</v>
       </c>
       <c r="AN302" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AO302" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AP302" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AQ302" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AR302" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AS302" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AT302" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AU302" t="n">
         <v>5</v>
@@ -66523,25 +66523,25 @@
         <v>1.4</v>
       </c>
       <c r="AN303" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AO303" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AP303" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AQ303" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AR303" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AS303" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AT303" t="n">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="AU303" t="n">
         <v>5</v>
@@ -66741,25 +66741,25 @@
         <v>1.85</v>
       </c>
       <c r="AN304" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AO304" t="n">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="AP304" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ304" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AR304" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AS304" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AT304" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="AU304" t="n">
         <v>9</v>
@@ -66959,25 +66959,25 @@
         <v>1.18</v>
       </c>
       <c r="AN305" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AO305" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AP305" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AQ305" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AR305" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AS305" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT305" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AU305" t="n">
         <v>2</v>
@@ -67177,25 +67177,25 @@
         <v>1.65</v>
       </c>
       <c r="AN306" t="n">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="AO306" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AP306" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AQ306" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AR306" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AS306" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AT306" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AU306" t="n">
         <v>8</v>
@@ -67395,25 +67395,25 @@
         <v>1.3</v>
       </c>
       <c r="AN307" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AO307" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AP307" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AQ307" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AR307" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AS307" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT307" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="AU307" t="n">
         <v>2</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany 2. Bundesliga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Germany 2. Bundesliga_20242025.xlsx
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,19 +2873,19 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
@@ -3085,25 +3085,25 @@
         <v>1.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
@@ -3306,22 +3306,22 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
         <v>5</v>
@@ -3521,25 +3521,25 @@
         <v>1.29</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -3739,25 +3739,25 @@
         <v>1.85</v>
       </c>
       <c r="AN15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
         <v>5</v>
@@ -3957,25 +3957,25 @@
         <v>1.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
         <v>2</v>
@@ -4175,25 +4175,25 @@
         <v>1.92</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
         <v>6</v>
@@ -4396,22 +4396,22 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -4614,22 +4614,22 @@
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
@@ -4829,25 +4829,25 @@
         <v>2.17</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>1</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AU20" t="n">
         <v>7</v>
@@ -5047,25 +5047,25 @@
         <v>1.55</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="AU21" t="n">
         <v>3</v>
@@ -5265,25 +5265,25 @@
         <v>1.47</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS22" t="n">
         <v>1.29</v>
       </c>
-      <c r="AS22" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AT22" t="n">
-        <v>2.77</v>
+        <v>2.42</v>
       </c>
       <c r="AU22" t="n">
         <v>6</v>
@@ -5483,25 +5483,25 @@
         <v>1.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AT23" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="AU23" t="n">
         <v>3</v>
@@ -5701,25 +5701,25 @@
         <v>2.15</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
@@ -5919,25 +5919,25 @@
         <v>2.55</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.71</v>
+        <v>3.41</v>
       </c>
       <c r="AU25" t="n">
         <v>13</v>
@@ -6140,22 +6140,22 @@
         <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="AU26" t="n">
         <v>8</v>
@@ -6358,22 +6358,22 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
@@ -6573,25 +6573,25 @@
         <v>1.57</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.91</v>
+        <v>3.26</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
@@ -6791,25 +6791,25 @@
         <v>1.67</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="AU29" t="n">
         <v>5</v>
@@ -7009,25 +7009,25 @@
         <v>1.38</v>
       </c>
       <c r="AN30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.88</v>
+        <v>0.66</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="AU30" t="n">
         <v>6</v>
@@ -7227,25 +7227,25 @@
         <v>2.95</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -7445,25 +7445,25 @@
         <v>1.54</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AS32" t="n">
         <v>1.58</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AU32" t="n">
         <v>5</v>
@@ -7663,25 +7663,25 @@
         <v>1.45</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.48</v>
+        <v>0.97</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AU33" t="n">
         <v>3</v>
@@ -7881,25 +7881,25 @@
         <v>1.62</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS34" t="n">
         <v>1.32</v>
       </c>
-      <c r="AS34" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AT34" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="AU34" t="n">
         <v>10</v>
@@ -8099,25 +8099,25 @@
         <v>2.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.33</v>
+        <v>0.96</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="AU35" t="n">
         <v>1</v>
@@ -8317,25 +8317,25 @@
         <v>1.41</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="AU36" t="n">
         <v>5</v>
@@ -8538,22 +8538,22 @@
         <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.35</v>
+        <v>2.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AU37" t="n">
         <v>1</v>
@@ -8753,25 +8753,25 @@
         <v>1.36</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO38" t="n">
         <v>2</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AU38" t="n">
         <v>4</v>
@@ -8971,25 +8971,25 @@
         <v>2</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AO39" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="AU39" t="n">
         <v>5</v>
@@ -9189,25 +9189,25 @@
         <v>1.85</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="AU40" t="n">
         <v>9</v>
@@ -9407,25 +9407,25 @@
         <v>1.6</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.09</v>
+        <v>2.41</v>
       </c>
       <c r="AU41" t="n">
         <v>3</v>
@@ -9625,25 +9625,25 @@
         <v>2</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AU42" t="n">
         <v>3</v>
@@ -9843,25 +9843,25 @@
         <v>2.65</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="AU43" t="n">
         <v>13</v>
@@ -10064,22 +10064,22 @@
         <v>2</v>
       </c>
       <c r="AO44" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.96</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="AU44" t="n">
         <v>2</v>
@@ -10279,25 +10279,25 @@
         <v>1.5</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AO45" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AU45" t="n">
         <v>5</v>
@@ -10497,25 +10497,25 @@
         <v>3.25</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO46" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AU46" t="n">
         <v>8</v>
@@ -10715,25 +10715,25 @@
         <v>1.69</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO47" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.29</v>
+        <v>0.96</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="AU47" t="n">
         <v>5</v>
@@ -10933,25 +10933,25 @@
         <v>2.05</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AS48" t="n">
         <v>1.46</v>
       </c>
       <c r="AT48" t="n">
-        <v>2.83</v>
+        <v>3.03</v>
       </c>
       <c r="AU48" t="n">
         <v>7</v>
@@ -11151,25 +11151,25 @@
         <v>1.38</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AO49" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AP49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS49" t="n">
         <v>1.56</v>
       </c>
-      <c r="AQ49" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AT49" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AU49" t="n">
         <v>5</v>
@@ -11369,25 +11369,25 @@
         <v>1.38</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AO50" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR50" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="AU50" t="n">
         <v>3</v>
@@ -11587,25 +11587,25 @@
         <v>1.72</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="AU51" t="n">
         <v>9</v>
@@ -11805,25 +11805,25 @@
         <v>1.35</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO52" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="AU52" t="n">
         <v>4</v>
@@ -12023,25 +12023,25 @@
         <v>1.85</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AO53" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.19</v>
+        <v>0.93</v>
       </c>
       <c r="AT53" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AU53" t="n">
         <v>4</v>
@@ -12241,25 +12241,25 @@
         <v>1.42</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="AO54" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.39</v>
+        <v>1.74</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AU54" t="n">
         <v>4</v>
@@ -12459,25 +12459,25 @@
         <v>1.55</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO55" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR55" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AU55" t="n">
         <v>4</v>
@@ -12677,25 +12677,25 @@
         <v>1.56</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="AU56" t="n">
         <v>6</v>
@@ -12895,25 +12895,25 @@
         <v>1.35</v>
       </c>
       <c r="AN57" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AO57" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR57" t="n">
         <v>1.36</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AU57" t="n">
         <v>1</v>
@@ -13113,25 +13113,25 @@
         <v>2</v>
       </c>
       <c r="AN58" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AO58" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AT58" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AU58" t="n">
         <v>9</v>
@@ -13331,25 +13331,25 @@
         <v>1.33</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO59" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AU59" t="n">
         <v>2</v>
@@ -13549,25 +13549,25 @@
         <v>1.65</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AO60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AT60" t="n">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="AU60" t="n">
         <v>7</v>
@@ -13767,25 +13767,25 @@
         <v>1.4</v>
       </c>
       <c r="AN61" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AO61" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AT61" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="AU61" t="n">
         <v>3</v>
@@ -13985,25 +13985,25 @@
         <v>2.3</v>
       </c>
       <c r="AN62" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO62" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AS62" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AU62" t="n">
         <v>5</v>
@@ -14203,25 +14203,25 @@
         <v>2</v>
       </c>
       <c r="AN63" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AO63" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AT63" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="AU63" t="n">
         <v>6</v>
@@ -14421,25 +14421,25 @@
         <v>2.2</v>
       </c>
       <c r="AN64" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO64" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR64" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.23</v>
+        <v>0.96</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AU64" t="n">
         <v>5</v>
@@ -14639,25 +14639,25 @@
         <v>2.8</v>
       </c>
       <c r="AN65" t="n">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO65" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="AT65" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AU65" t="n">
         <v>9</v>
@@ -14857,25 +14857,25 @@
         <v>2.05</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="AO66" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AS66" t="n">
         <v>1.49</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="AU66" t="n">
         <v>5</v>
@@ -15075,25 +15075,25 @@
         <v>3.3</v>
       </c>
       <c r="AN67" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AO67" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR67" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AT67" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="AU67" t="n">
         <v>4</v>
@@ -15293,25 +15293,25 @@
         <v>1.57</v>
       </c>
       <c r="AN68" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AO68" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="AU68" t="n">
         <v>4</v>
@@ -15514,22 +15514,22 @@
         <v>1</v>
       </c>
       <c r="AO69" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR69" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AT69" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AU69" t="n">
         <v>7</v>
@@ -15732,22 +15732,22 @@
         <v>1</v>
       </c>
       <c r="AO70" t="n">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AT70" t="n">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="AU70" t="n">
         <v>1</v>
@@ -15947,25 +15947,25 @@
         <v>1.8</v>
       </c>
       <c r="AN71" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="AO71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP71" t="n">
         <v>1.29</v>
       </c>
-      <c r="AP71" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AQ71" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AT71" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AU71" t="n">
         <v>3</v>
@@ -16165,25 +16165,25 @@
         <v>1.4</v>
       </c>
       <c r="AN72" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AO72" t="n">
-        <v>1.86</v>
+        <v>0.33</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AT72" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="AU72" t="n">
         <v>9</v>
@@ -16383,25 +16383,25 @@
         <v>1.56</v>
       </c>
       <c r="AN73" t="n">
-        <v>2.43</v>
+        <v>1.67</v>
       </c>
       <c r="AO73" t="n">
-        <v>1.71</v>
+        <v>1.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AT73" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="AU73" t="n">
         <v>11</v>
@@ -16601,25 +16601,25 @@
         <v>0</v>
       </c>
       <c r="AN74" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AO74" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AT74" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="AU74" t="n">
         <v>1</v>
@@ -16819,25 +16819,25 @@
         <v>2</v>
       </c>
       <c r="AN75" t="n">
-        <v>1.38</v>
+        <v>0.75</v>
       </c>
       <c r="AO75" t="n">
-        <v>0.88</v>
+        <v>0.25</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ75" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS75" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR75" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AT75" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AU75" t="n">
         <v>5</v>
@@ -17037,25 +17037,25 @@
         <v>1.57</v>
       </c>
       <c r="AN76" t="n">
-        <v>0.63</v>
+        <v>0.5</v>
       </c>
       <c r="AO76" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="AU76" t="n">
         <v>1</v>
@@ -17255,22 +17255,22 @@
         <v>0</v>
       </c>
       <c r="AN77" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO77" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR77" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AT77" t="n">
         <v>2.26</v>
@@ -17473,25 +17473,25 @@
         <v>2.05</v>
       </c>
       <c r="AN78" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="AO78" t="n">
         <v>1</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AT78" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AU78" t="n">
         <v>3</v>
@@ -17691,25 +17691,25 @@
         <v>1.44</v>
       </c>
       <c r="AN79" t="n">
-        <v>1.13</v>
+        <v>0.67</v>
       </c>
       <c r="AO79" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="AU79" t="n">
         <v>8</v>
@@ -17909,25 +17909,25 @@
         <v>1.36</v>
       </c>
       <c r="AN80" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="AO80" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP80" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AU80" t="n">
         <v>2</v>
@@ -18130,22 +18130,22 @@
         <v>1.25</v>
       </c>
       <c r="AO81" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AU81" t="n">
         <v>4</v>
@@ -18345,25 +18345,25 @@
         <v>2.25</v>
       </c>
       <c r="AN82" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="AU82" t="n">
         <v>2</v>
@@ -18563,25 +18563,25 @@
         <v>2.15</v>
       </c>
       <c r="AN83" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AO83" t="n">
-        <v>1.78</v>
+        <v>1.2</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AT83" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AU83" t="n">
         <v>3</v>
@@ -18781,25 +18781,25 @@
         <v>2.03</v>
       </c>
       <c r="AN84" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AO84" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="AT84" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AU84" t="n">
         <v>13</v>
@@ -18999,25 +18999,25 @@
         <v>1.76</v>
       </c>
       <c r="AN85" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AO85" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.67</v>
+        <v>2.96</v>
       </c>
       <c r="AU85" t="n">
         <v>2</v>
@@ -19217,25 +19217,25 @@
         <v>1.85</v>
       </c>
       <c r="AN86" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AO86" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.51</v>
+        <v>2.71</v>
       </c>
       <c r="AU86" t="n">
         <v>6</v>
@@ -19435,25 +19435,25 @@
         <v>1.33</v>
       </c>
       <c r="AN87" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AO87" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR87" t="n">
         <v>1.2</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AU87" t="n">
         <v>10</v>
@@ -19653,25 +19653,25 @@
         <v>2.05</v>
       </c>
       <c r="AN88" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO88" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AT88" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AU88" t="n">
         <v>7</v>
@@ -19874,22 +19874,22 @@
         <v>1</v>
       </c>
       <c r="AO89" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.16</v>
+        <v>0.93</v>
       </c>
       <c r="AT89" t="n">
-        <v>2.58</v>
+        <v>2.22</v>
       </c>
       <c r="AU89" t="n">
         <v>5</v>
@@ -20089,25 +20089,25 @@
         <v>1.48</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.78</v>
+        <v>1</v>
       </c>
       <c r="AO90" t="n">
-        <v>1.78</v>
+        <v>0.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AT90" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="AU90" t="n">
         <v>5</v>
@@ -20307,25 +20307,25 @@
         <v>1.75</v>
       </c>
       <c r="AN91" t="n">
-        <v>0.78</v>
+        <v>1.5</v>
       </c>
       <c r="AO91" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AT91" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="AU91" t="n">
         <v>2</v>
@@ -20525,25 +20525,25 @@
         <v>1.3</v>
       </c>
       <c r="AN92" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AO92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="AU92" t="n">
         <v>4</v>
@@ -20743,25 +20743,25 @@
         <v>1.52</v>
       </c>
       <c r="AN93" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AO93" t="n">
         <v>0.8</v>
       </c>
       <c r="AP93" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="AU93" t="n">
         <v>5</v>
@@ -20961,25 +20961,25 @@
         <v>1.25</v>
       </c>
       <c r="AN94" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO94" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AP94" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AT94" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AU94" t="n">
         <v>2</v>
@@ -21179,25 +21179,25 @@
         <v>1.57</v>
       </c>
       <c r="AN95" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AO95" t="n">
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT95" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="AU95" t="n">
         <v>5</v>
@@ -21397,25 +21397,25 @@
         <v>1.77</v>
       </c>
       <c r="AN96" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AO96" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AT96" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="AU96" t="n">
         <v>8</v>
@@ -21615,25 +21615,25 @@
         <v>1.4</v>
       </c>
       <c r="AN97" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AO97" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AS97" t="n">
         <v>1.82</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="AU97" t="n">
         <v>4</v>
@@ -21833,25 +21833,25 @@
         <v>1.65</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AO98" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AU98" t="n">
         <v>6</v>
@@ -22051,25 +22051,25 @@
         <v>2.15</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AO99" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AU99" t="n">
         <v>2</v>
@@ -22269,25 +22269,25 @@
         <v>2.5</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AO100" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="AU100" t="n">
         <v>4</v>
@@ -22487,25 +22487,25 @@
         <v>1.3</v>
       </c>
       <c r="AN101" t="n">
-        <v>0.82</v>
+        <v>1.4</v>
       </c>
       <c r="AO101" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="AU101" t="n">
         <v>4</v>
@@ -22705,25 +22705,25 @@
         <v>1.57</v>
       </c>
       <c r="AN102" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AO102" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="AU102" t="n">
         <v>5</v>
@@ -22923,25 +22923,25 @@
         <v>2.9</v>
       </c>
       <c r="AN103" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AO103" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="AU103" t="n">
         <v>1</v>
@@ -23141,22 +23141,22 @@
         <v>1.62</v>
       </c>
       <c r="AN104" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AO104" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AT104" t="n">
         <v>2.81</v>
@@ -23359,25 +23359,25 @@
         <v>1.93</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="AO105" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.16</v>
+        <v>0.9</v>
       </c>
       <c r="AT105" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU105" t="n">
         <v>8</v>
@@ -23577,25 +23577,25 @@
         <v>1.67</v>
       </c>
       <c r="AN106" t="n">
-        <v>1.82</v>
+        <v>1</v>
       </c>
       <c r="AO106" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="AU106" t="n">
         <v>3</v>
@@ -23795,25 +23795,25 @@
         <v>2.2</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AO107" t="n">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AT107" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AU107" t="n">
         <v>2</v>
@@ -24013,25 +24013,25 @@
         <v>2.45</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AO108" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AU108" t="n">
         <v>4</v>
@@ -24231,25 +24231,25 @@
         <v>1.45</v>
       </c>
       <c r="AN109" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AO109" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AU109" t="n">
         <v>9</v>
@@ -24449,25 +24449,25 @@
         <v>1.83</v>
       </c>
       <c r="AN110" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AO110" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AU110" t="n">
         <v>5</v>
@@ -24667,25 +24667,25 @@
         <v>1.18</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AO111" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AU111" t="n">
         <v>1</v>
@@ -24885,25 +24885,25 @@
         <v>1.47</v>
       </c>
       <c r="AN112" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AO112" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AU112" t="n">
         <v>5</v>
@@ -25103,25 +25103,25 @@
         <v>2.15</v>
       </c>
       <c r="AN113" t="n">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="AO113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS113" t="n">
         <v>0.83</v>
       </c>
-      <c r="AP113" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ113" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AR113" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AS113" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AT113" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="AU113" t="n">
         <v>-1</v>
@@ -25321,25 +25321,25 @@
         <v>1.78</v>
       </c>
       <c r="AN114" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="AO114" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AT114" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AU114" t="n">
         <v>-1</v>
@@ -25539,25 +25539,25 @@
         <v>1.85</v>
       </c>
       <c r="AN115" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="AO115" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP115" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ115" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR115" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ115" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR115" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AS115" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.82</v>
+        <v>3.11</v>
       </c>
       <c r="AU115" t="n">
         <v>-1</v>
@@ -25757,25 +25757,25 @@
         <v>2.15</v>
       </c>
       <c r="AN116" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AO116" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="AU116" t="n">
         <v>8</v>
@@ -25975,25 +25975,25 @@
         <v>1.72</v>
       </c>
       <c r="AN117" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AO117" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="AU117" t="n">
         <v>7</v>
@@ -26193,25 +26193,25 @@
         <v>1.3</v>
       </c>
       <c r="AN118" t="n">
-        <v>0.58</v>
+        <v>1.17</v>
       </c>
       <c r="AO118" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="AP118" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR118" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="AU118" t="n">
         <v>0</v>
@@ -26411,25 +26411,25 @@
         <v>1.47</v>
       </c>
       <c r="AN119" t="n">
-        <v>1.62</v>
+        <v>0.83</v>
       </c>
       <c r="AO119" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="AU119" t="n">
         <v>2</v>
@@ -26629,25 +26629,25 @@
         <v>1.7</v>
       </c>
       <c r="AN120" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO120" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR120" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS120" t="n">
         <v>1.18</v>
       </c>
-      <c r="AS120" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AT120" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="AU120" t="n">
         <v>5</v>
@@ -26847,25 +26847,25 @@
         <v>2</v>
       </c>
       <c r="AN121" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AO121" t="n">
-        <v>1.69</v>
+        <v>0.67</v>
       </c>
       <c r="AP121" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR121" t="n">
         <v>1.79</v>
       </c>
-      <c r="AQ121" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR121" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AS121" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AT121" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AU121" t="n">
         <v>3</v>
@@ -27065,25 +27065,25 @@
         <v>1.55</v>
       </c>
       <c r="AN122" t="n">
-        <v>1.69</v>
+        <v>2.17</v>
       </c>
       <c r="AO122" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AU122" t="n">
         <v>2</v>
@@ -27283,25 +27283,25 @@
         <v>2.35</v>
       </c>
       <c r="AN123" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS123" t="n">
         <v>0.92</v>
       </c>
-      <c r="AO123" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AP123" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ123" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR123" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AS123" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AT123" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AU123" t="n">
         <v>1</v>
@@ -27501,22 +27501,22 @@
         <v>2</v>
       </c>
       <c r="AN124" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AO124" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AT124" t="n">
         <v>2.58</v>
@@ -27719,25 +27719,25 @@
         <v>1.52</v>
       </c>
       <c r="AN125" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AO125" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AT125" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="AU125" t="n">
         <v>4</v>
@@ -27937,25 +27937,25 @@
         <v>1.45</v>
       </c>
       <c r="AN126" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AO126" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT126" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AU126" t="n">
         <v>4</v>
@@ -28155,25 +28155,25 @@
         <v>1.57</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="AO127" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP127" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="AU127" t="n">
         <v>3</v>
@@ -28373,22 +28373,22 @@
         <v>1.66</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AO128" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AT128" t="n">
         <v>2.62</v>
@@ -28591,25 +28591,25 @@
         <v>1.95</v>
       </c>
       <c r="AN129" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="AO129" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ129" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="AU129" t="n">
         <v>4</v>
@@ -28809,25 +28809,25 @@
         <v>1.53</v>
       </c>
       <c r="AN130" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AO130" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AU130" t="n">
         <v>5</v>
@@ -29027,25 +29027,25 @@
         <v>1.38</v>
       </c>
       <c r="AN131" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AO131" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="AU131" t="n">
         <v>6</v>
@@ -29245,25 +29245,25 @@
         <v>2.35</v>
       </c>
       <c r="AN132" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="AO132" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AP132" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR132" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ132" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AS132" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AU132" t="n">
         <v>10</v>
@@ -29466,22 +29466,22 @@
         <v>0.86</v>
       </c>
       <c r="AO133" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="AP133" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS133" t="n">
         <v>1.06</v>
       </c>
-      <c r="AQ133" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AT133" t="n">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="AU133" t="n">
         <v>4</v>
@@ -29681,25 +29681,25 @@
         <v>1.83</v>
       </c>
       <c r="AN134" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AO134" t="n">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AU134" t="n">
         <v>7</v>
@@ -29899,25 +29899,25 @@
         <v>2</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.57</v>
+        <v>0.86</v>
       </c>
       <c r="AO135" t="n">
-        <v>0.93</v>
+        <v>0.29</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.1</v>
+        <v>0.99</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AU135" t="n">
         <v>7</v>
@@ -30117,25 +30117,25 @@
         <v>1.06</v>
       </c>
       <c r="AN136" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AO136" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AU136" t="n">
         <v>2</v>
@@ -30335,25 +30335,25 @@
         <v>2.9</v>
       </c>
       <c r="AN137" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AO137" t="n">
-        <v>0.53</v>
+        <v>0.14</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AU137" t="n">
         <v>8</v>
@@ -30553,25 +30553,25 @@
         <v>2.2</v>
       </c>
       <c r="AN138" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO138" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AU138" t="n">
         <v>4</v>
@@ -30771,25 +30771,25 @@
         <v>1.47</v>
       </c>
       <c r="AN139" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AO139" t="n">
-        <v>1.67</v>
+        <v>2.29</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ139" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AT139" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AU139" t="n">
         <v>10</v>
@@ -30989,25 +30989,25 @@
         <v>1.47</v>
       </c>
       <c r="AN140" t="n">
-        <v>1.6</v>
+        <v>0.71</v>
       </c>
       <c r="AO140" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU140" t="n">
         <v>4</v>
@@ -31207,25 +31207,25 @@
         <v>1.2</v>
       </c>
       <c r="AN141" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="AO141" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AP141" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AT141" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="AU141" t="n">
         <v>4</v>
@@ -31425,25 +31425,25 @@
         <v>1.85</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AO142" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AP142" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ142" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ142" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AR142" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AS142" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="AU142" t="n">
         <v>12</v>
@@ -31643,25 +31643,25 @@
         <v>2.2</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AO143" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="AU143" t="n">
         <v>5</v>
@@ -31861,25 +31861,25 @@
         <v>1.42</v>
       </c>
       <c r="AN144" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AO144" t="n">
-        <v>1.73</v>
+        <v>0.71</v>
       </c>
       <c r="AP144" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AT144" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="AU144" t="n">
         <v>2</v>
@@ -32079,25 +32079,25 @@
         <v>1.42</v>
       </c>
       <c r="AN145" t="n">
-        <v>0.87</v>
+        <v>1.57</v>
       </c>
       <c r="AO145" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AU145" t="n">
         <v>2</v>
@@ -32297,25 +32297,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO146" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AT146" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AU146" t="n">
         <v>5</v>
@@ -32515,25 +32515,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147" t="n">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="AO147" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AU147" t="n">
         <v>6</v>
@@ -32733,25 +32733,25 @@
         <v>2.35</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AO148" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="AU148" t="n">
         <v>9</v>
@@ -32951,25 +32951,25 @@
         <v>1.66</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="AO149" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR149" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="AU149" t="n">
         <v>1</v>
@@ -33169,25 +33169,25 @@
         <v>1.72</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO150" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR150" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AT150" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AU150" t="n">
         <v>10</v>
@@ -33387,25 +33387,25 @@
         <v>1.95</v>
       </c>
       <c r="AN151" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AO151" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ151" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS151" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR151" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS151" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AT151" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="AU151" t="n">
         <v>5</v>
@@ -33605,25 +33605,25 @@
         <v>1.17</v>
       </c>
       <c r="AN152" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AO152" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="AU152" t="n">
         <v>5</v>
@@ -33823,25 +33823,25 @@
         <v>1.7</v>
       </c>
       <c r="AN153" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR153" t="n">
         <v>1.63</v>
       </c>
-      <c r="AO153" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AP153" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ153" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR153" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AS153" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.67</v>
+        <v>3.02</v>
       </c>
       <c r="AU153" t="n">
         <v>1</v>
@@ -34041,25 +34041,25 @@
         <v>1.2</v>
       </c>
       <c r="AN154" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AO154" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AP154" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR154" t="n">
         <v>1.56</v>
       </c>
-      <c r="AQ154" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR154" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AS154" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="AU154" t="n">
         <v>4</v>
@@ -34259,25 +34259,25 @@
         <v>1.57</v>
       </c>
       <c r="AN155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP155" t="n">
         <v>1.53</v>
       </c>
-      <c r="AO155" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AP155" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AQ155" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AU155" t="n">
         <v>6</v>
@@ -34477,25 +34477,25 @@
         <v>1.23</v>
       </c>
       <c r="AN156" t="n">
-        <v>0.65</v>
+        <v>1.11</v>
       </c>
       <c r="AO156" t="n">
-        <v>1.59</v>
+        <v>0.63</v>
       </c>
       <c r="AP156" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AU156" t="n">
         <v>1</v>
@@ -34695,25 +34695,25 @@
         <v>1.83</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AO157" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ157" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS157" t="n">
         <v>0.88</v>
       </c>
-      <c r="AR157" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AS157" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AT157" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AU157" t="n">
         <v>9</v>
@@ -34913,25 +34913,25 @@
         <v>1.37</v>
       </c>
       <c r="AN158" t="n">
-        <v>0.76</v>
+        <v>1.38</v>
       </c>
       <c r="AO158" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AU158" t="n">
         <v>1</v>
@@ -35131,25 +35131,25 @@
         <v>1.53</v>
       </c>
       <c r="AN159" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ159" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AO159" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AP159" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AQ159" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AR159" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="AU159" t="n">
         <v>4</v>
@@ -35349,25 +35349,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AO160" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AP160" t="n">
         <v>1.82</v>
       </c>
-      <c r="AP160" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AQ160" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AT160" t="n">
-        <v>3.06</v>
+        <v>3.09</v>
       </c>
       <c r="AU160" t="n">
         <v>5</v>
@@ -35567,25 +35567,25 @@
         <v>1.7</v>
       </c>
       <c r="AN161" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AO161" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AS161" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AT161" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU161" t="n">
         <v>7</v>
@@ -35785,25 +35785,25 @@
         <v>1.63</v>
       </c>
       <c r="AN162" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AO162" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="AU162" t="n">
         <v>4</v>
@@ -36003,25 +36003,25 @@
         <v>1.6</v>
       </c>
       <c r="AN163" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AO163" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR163" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AT163" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AU163" t="n">
         <v>7</v>
@@ -36221,25 +36221,25 @@
         <v>2.15</v>
       </c>
       <c r="AN164" t="n">
-        <v>1.72</v>
+        <v>0.75</v>
       </c>
       <c r="AO164" t="n">
-        <v>0.78</v>
+        <v>0.22</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="AT164" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="AU164" t="n">
         <v>5</v>
@@ -36439,25 +36439,25 @@
         <v>1.55</v>
       </c>
       <c r="AN165" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AP165" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AT165" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AU165" t="n">
         <v>4</v>
@@ -36657,25 +36657,25 @@
         <v>2.15</v>
       </c>
       <c r="AN166" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AO166" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AU166" t="n">
         <v>5</v>
@@ -36875,25 +36875,25 @@
         <v>1.58</v>
       </c>
       <c r="AN167" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AO167" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR167" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="AU167" t="n">
         <v>4</v>
@@ -37093,25 +37093,25 @@
         <v>1.73</v>
       </c>
       <c r="AN168" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO168" t="n">
-        <v>1.39</v>
+        <v>0.89</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR168" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AT168" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AU168" t="n">
         <v>5</v>
@@ -37311,25 +37311,25 @@
         <v>1.46</v>
       </c>
       <c r="AN169" t="n">
-        <v>1.39</v>
+        <v>0.88</v>
       </c>
       <c r="AO169" t="n">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AU169" t="n">
         <v>5</v>
@@ -37529,25 +37529,25 @@
         <v>1.83</v>
       </c>
       <c r="AN170" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AO170" t="n">
-        <v>0.61</v>
+        <v>0.13</v>
       </c>
       <c r="AP170" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ170" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AU170" t="n">
         <v>7</v>
@@ -37747,25 +37747,25 @@
         <v>1.68</v>
       </c>
       <c r="AN171" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AO171" t="n">
         <v>1.56</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.91</v>
+        <v>2.68</v>
       </c>
       <c r="AU171" t="n">
         <v>4</v>
@@ -37965,25 +37965,25 @@
         <v>2.2</v>
       </c>
       <c r="AN172" t="n">
-        <v>1.67</v>
+        <v>2.44</v>
       </c>
       <c r="AO172" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT172" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="AU172" t="n">
         <v>6</v>
@@ -38183,25 +38183,25 @@
         <v>1.63</v>
       </c>
       <c r="AN173" t="n">
-        <v>1.32</v>
+        <v>1.89</v>
       </c>
       <c r="AO173" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AP173" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="AU173" t="n">
         <v>6</v>
@@ -38401,25 +38401,25 @@
         <v>1.69</v>
       </c>
       <c r="AN174" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AO174" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ174" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AU174" t="n">
         <v>6</v>
@@ -38619,25 +38619,25 @@
         <v>1.24</v>
       </c>
       <c r="AN175" t="n">
-        <v>0.58</v>
+        <v>1</v>
       </c>
       <c r="AO175" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="AP175" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AS175" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AT175" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AU175" t="n">
         <v>2</v>
@@ -38837,25 +38837,25 @@
         <v>1.2</v>
       </c>
       <c r="AN176" t="n">
-        <v>0.79</v>
+        <v>1.33</v>
       </c>
       <c r="AO176" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AS176" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT176" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="AU176" t="n">
         <v>4</v>
@@ -39055,25 +39055,25 @@
         <v>2.1</v>
       </c>
       <c r="AN177" t="n">
-        <v>1.58</v>
+        <v>1</v>
       </c>
       <c r="AO177" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AS177" t="n">
-        <v>1.18</v>
+        <v>0.98</v>
       </c>
       <c r="AT177" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AU177" t="n">
         <v>3</v>
@@ -39273,22 +39273,22 @@
         <v>1.58</v>
       </c>
       <c r="AN178" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AO178" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR178" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AS178" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AT178" t="n">
         <v>2.77</v>
@@ -39491,25 +39491,25 @@
         <v>2.1</v>
       </c>
       <c r="AN179" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AO179" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR179" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AS179" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AT179" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="AU179" t="n">
         <v>7</v>
@@ -39709,25 +39709,25 @@
         <v>1.87</v>
       </c>
       <c r="AN180" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AO180" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR180" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AS180" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT180" t="n">
-        <v>2.53</v>
+        <v>2.72</v>
       </c>
       <c r="AU180" t="n">
         <v>4</v>
@@ -39927,25 +39927,25 @@
         <v>1.88</v>
       </c>
       <c r="AN181" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AO181" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR181" t="n">
         <v>1.63</v>
       </c>
-      <c r="AP181" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AQ181" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR181" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AS181" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="AT181" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="AU181" t="n">
         <v>3</v>
@@ -40148,22 +40148,22 @@
         <v>1</v>
       </c>
       <c r="AO182" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR182" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AS182" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AT182" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AU182" t="n">
         <v>3</v>
@@ -40363,22 +40363,22 @@
         <v>1.93</v>
       </c>
       <c r="AN183" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AO183" t="n">
-        <v>0.7</v>
+        <v>0.11</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ183" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR183" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AS183" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AT183" t="n">
         <v>2.24</v>
@@ -40581,25 +40581,25 @@
         <v>1.68</v>
       </c>
       <c r="AN184" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AO184" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR184" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AS184" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AT184" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="AU184" t="n">
         <v>2</v>
@@ -40799,25 +40799,25 @@
         <v>1.68</v>
       </c>
       <c r="AN185" t="n">
-        <v>1.75</v>
+        <v>0.78</v>
       </c>
       <c r="AO185" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR185" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AS185" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT185" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AU185" t="n">
         <v>8</v>
@@ -41017,25 +41017,25 @@
         <v>1.41</v>
       </c>
       <c r="AN186" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AO186" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AP186" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR186" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AS186" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AT186" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AU186" t="n">
         <v>3</v>
@@ -41235,25 +41235,25 @@
         <v>1.95</v>
       </c>
       <c r="AN187" t="n">
-        <v>1.25</v>
+        <v>0.78</v>
       </c>
       <c r="AO187" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AP187" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR187" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AS187" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AT187" t="n">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AU187" t="n">
         <v>5</v>
@@ -41453,25 +41453,25 @@
         <v>2</v>
       </c>
       <c r="AN188" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AO188" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR188" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AS188" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT188" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AU188" t="n">
         <v>3</v>
@@ -41671,25 +41671,25 @@
         <v>1.95</v>
       </c>
       <c r="AN189" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AO189" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR189" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AS189" t="n">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="AT189" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="AU189" t="n">
         <v>4</v>
@@ -41889,25 +41889,25 @@
         <v>1.72</v>
       </c>
       <c r="AN190" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AO190" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR190" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AT190" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="AU190" t="n">
         <v>2</v>
@@ -42107,25 +42107,25 @@
         <v>1.42</v>
       </c>
       <c r="AN191" t="n">
-        <v>1.67</v>
+        <v>0.7</v>
       </c>
       <c r="AO191" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ191" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR191" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AS191" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AT191" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AU191" t="n">
         <v>7</v>
@@ -42325,25 +42325,25 @@
         <v>2.05</v>
       </c>
       <c r="AN192" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AO192" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AS192" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.52</v>
+        <v>2.71</v>
       </c>
       <c r="AU192" t="n">
         <v>6</v>
@@ -42543,25 +42543,25 @@
         <v>2</v>
       </c>
       <c r="AN193" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AO193" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR193" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AS193" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AT193" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="AU193" t="n">
         <v>4</v>
@@ -42761,25 +42761,25 @@
         <v>1.46</v>
       </c>
       <c r="AN194" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AO194" t="n">
-        <v>1.57</v>
+        <v>0.9</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR194" t="n">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AS194" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AT194" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AU194" t="n">
         <v>5</v>
@@ -42979,25 +42979,25 @@
         <v>1.43</v>
       </c>
       <c r="AN195" t="n">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="AO195" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR195" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AS195" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AT195" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="AU195" t="n">
         <v>9</v>
@@ -43197,25 +43197,25 @@
         <v>1.63</v>
       </c>
       <c r="AN196" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="AO196" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AU196" t="n">
         <v>3</v>
@@ -43415,25 +43415,25 @@
         <v>1.17</v>
       </c>
       <c r="AN197" t="n">
-        <v>0.67</v>
+        <v>1.18</v>
       </c>
       <c r="AO197" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AP197" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AU197" t="n">
         <v>5</v>
@@ -43633,25 +43633,25 @@
         <v>1.73</v>
       </c>
       <c r="AN198" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AO198" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AS198" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="AU198" t="n">
         <v>3</v>
@@ -43851,25 +43851,25 @@
         <v>1.9</v>
       </c>
       <c r="AN199" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AO199" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AU199" t="n">
         <v>6</v>
@@ -44069,25 +44069,25 @@
         <v>2.1</v>
       </c>
       <c r="AN200" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AO200" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AU200" t="n">
         <v>8</v>
@@ -44287,25 +44287,25 @@
         <v>1.71</v>
       </c>
       <c r="AN201" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="AO201" t="n">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ201" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ201" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AR201" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="AU201" t="n">
         <v>3</v>
@@ -44505,25 +44505,25 @@
         <v>1.42</v>
       </c>
       <c r="AN202" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AO202" t="n">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.34</v>
+        <v>1.58</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="AU202" t="n">
         <v>4</v>
@@ -44723,25 +44723,25 @@
         <v>1.38</v>
       </c>
       <c r="AN203" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="AO203" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AP203" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="AU203" t="n">
         <v>3</v>
@@ -44944,22 +44944,22 @@
         <v>0.91</v>
       </c>
       <c r="AO204" t="n">
-        <v>0.68</v>
+        <v>0.1</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ204" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AU204" t="n">
         <v>5</v>
@@ -45159,25 +45159,25 @@
         <v>1.65</v>
       </c>
       <c r="AN205" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AO205" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="AU205" t="n">
         <v>1</v>
@@ -45380,22 +45380,22 @@
         <v>1.82</v>
       </c>
       <c r="AO206" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AT206" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AU206" t="n">
         <v>4</v>
@@ -45595,25 +45595,25 @@
         <v>1.53</v>
       </c>
       <c r="AN207" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AO207" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="AU207" t="n">
         <v>3</v>
@@ -45813,25 +45813,25 @@
         <v>1.68</v>
       </c>
       <c r="AN208" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AO208" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AU208" t="n">
         <v>7</v>
@@ -46031,25 +46031,25 @@
         <v>1.98</v>
       </c>
       <c r="AN209" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AO209" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ209" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS209" t="n">
         <v>1.15</v>
       </c>
-      <c r="AR209" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS209" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AT209" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AU209" t="n">
         <v>4</v>
@@ -46249,25 +46249,25 @@
         <v>1.98</v>
       </c>
       <c r="AN210" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AO210" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR210" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AU210" t="n">
         <v>6</v>
@@ -46467,25 +46467,25 @@
         <v>1.53</v>
       </c>
       <c r="AN211" t="n">
-        <v>0.91</v>
+        <v>1.36</v>
       </c>
       <c r="AO211" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ211" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AS211" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AU211" t="n">
         <v>3</v>
@@ -46685,25 +46685,25 @@
         <v>2.15</v>
       </c>
       <c r="AN212" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AO212" t="n">
-        <v>0.65</v>
+        <v>0.09</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ212" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AT212" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AU212" t="n">
         <v>13</v>
@@ -46903,25 +46903,25 @@
         <v>1.46</v>
       </c>
       <c r="AN213" t="n">
-        <v>1.52</v>
+        <v>2.09</v>
       </c>
       <c r="AO213" t="n">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR213" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AS213" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AT213" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AU213" t="n">
         <v>2</v>
@@ -47121,25 +47121,25 @@
         <v>1.36</v>
       </c>
       <c r="AN214" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AO214" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AP214" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR214" t="n">
         <v>1.53</v>
       </c>
-      <c r="AQ214" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR214" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AS214" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AT214" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="AU214" t="n">
         <v>2</v>
@@ -47339,25 +47339,25 @@
         <v>1.82</v>
       </c>
       <c r="AN215" t="n">
-        <v>1.65</v>
+        <v>0.91</v>
       </c>
       <c r="AO215" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ215" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR215" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AS215" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AT215" t="n">
-        <v>2.96</v>
+        <v>3.17</v>
       </c>
       <c r="AU215" t="n">
         <v>10</v>
@@ -47557,25 +47557,25 @@
         <v>1.55</v>
       </c>
       <c r="AN216" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AO216" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AS216" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AT216" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AU216" t="n">
         <v>5</v>
@@ -47775,25 +47775,25 @@
         <v>1.5</v>
       </c>
       <c r="AN217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ217" t="n">
         <v>1.65</v>
       </c>
-      <c r="AO217" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AP217" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ217" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AR217" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AS217" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="AU217" t="n">
         <v>5</v>
@@ -47993,25 +47993,25 @@
         <v>1.85</v>
       </c>
       <c r="AN218" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO218" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP218" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ218" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ218" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AR218" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AS218" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AT218" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="AU218" t="n">
         <v>12</v>
@@ -48211,25 +48211,25 @@
         <v>1.53</v>
       </c>
       <c r="AN219" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AO219" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AP219" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ219" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR219" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AS219" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AT219" t="n">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="AU219" t="n">
         <v>1</v>
@@ -48429,25 +48429,25 @@
         <v>1.4</v>
       </c>
       <c r="AN220" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AO220" t="n">
-        <v>1.71</v>
+        <v>2.33</v>
       </c>
       <c r="AP220" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ220" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR220" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AS220" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AT220" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AU220" t="n">
         <v>2</v>
@@ -48647,25 +48647,25 @@
         <v>1.73</v>
       </c>
       <c r="AN221" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AO221" t="n">
         <v>1.08</v>
       </c>
-      <c r="AO221" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AP221" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ221" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR221" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AS221" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AT221" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="AU221" t="n">
         <v>5</v>
@@ -48865,25 +48865,25 @@
         <v>1.26</v>
       </c>
       <c r="AN222" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="AO222" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AP222" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR222" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AS222" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT222" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AU222" t="n">
         <v>1</v>
@@ -49083,25 +49083,25 @@
         <v>2.05</v>
       </c>
       <c r="AN223" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO223" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AP223" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ223" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR223" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AS223" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AT223" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AU223" t="n">
         <v>9</v>
@@ -49301,22 +49301,22 @@
         <v>2.3</v>
       </c>
       <c r="AN224" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="AO224" t="n">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
       <c r="AP224" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ224" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR224" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AS224" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AT224" t="n">
         <v>2.54</v>
@@ -49519,25 +49519,25 @@
         <v>1.49</v>
       </c>
       <c r="AN225" t="n">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AO225" t="n">
-        <v>1.46</v>
+        <v>1</v>
       </c>
       <c r="AP225" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR225" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AT225" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="AU225" t="n">
         <v>4</v>
@@ -49737,25 +49737,25 @@
         <v>1.2</v>
       </c>
       <c r="AN226" t="n">
-        <v>0.63</v>
+        <v>1.17</v>
       </c>
       <c r="AO226" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AP226" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ226" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR226" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AS226" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AT226" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="AU226" t="n">
         <v>0</v>
@@ -49955,25 +49955,25 @@
         <v>1.51</v>
       </c>
       <c r="AN227" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AO227" t="n">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="AP227" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ227" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR227" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AS227" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AT227" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="AU227" t="n">
         <v>4</v>
@@ -50173,25 +50173,25 @@
         <v>1.5</v>
       </c>
       <c r="AN228" t="n">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="AO228" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP228" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ228" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR228" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AS228" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT228" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="AU228" t="n">
         <v>10</v>
@@ -50391,25 +50391,25 @@
         <v>2.18</v>
       </c>
       <c r="AN229" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AO229" t="n">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="AP229" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ229" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR229" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AS229" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AT229" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="AU229" t="n">
         <v>4</v>
@@ -50609,25 +50609,25 @@
         <v>2.02</v>
       </c>
       <c r="AN230" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AO230" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AP230" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ230" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR230" t="n">
         <v>1.56</v>
       </c>
-      <c r="AR230" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AS230" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="AT230" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AU230" t="n">
         <v>8</v>
@@ -50827,25 +50827,25 @@
         <v>2.32</v>
       </c>
       <c r="AN231" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="AO231" t="n">
-        <v>0.64</v>
+        <v>0.08</v>
       </c>
       <c r="AP231" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ231" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR231" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AS231" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AT231" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AU231" t="n">
         <v>9</v>
@@ -51045,25 +51045,25 @@
         <v>1.82</v>
       </c>
       <c r="AN232" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AO232" t="n">
-        <v>1.24</v>
+        <v>1</v>
       </c>
       <c r="AP232" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ232" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR232" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AS232" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AT232" t="n">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="AU232" t="n">
         <v>5</v>
@@ -51263,25 +51263,25 @@
         <v>1.72</v>
       </c>
       <c r="AN233" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AO233" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ233" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR233" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS233" t="n">
         <v>1.15</v>
       </c>
-      <c r="AR233" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AS233" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AT233" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AU233" t="n">
         <v>3</v>
@@ -51481,25 +51481,25 @@
         <v>1.72</v>
       </c>
       <c r="AN234" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AO234" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AP234" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ234" t="n">
         <v>0.76</v>
       </c>
-      <c r="AP234" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AQ234" t="n">
-        <v>0.88</v>
-      </c>
       <c r="AR234" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AS234" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT234" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AU234" t="n">
         <v>5</v>
@@ -51699,25 +51699,25 @@
         <v>1.36</v>
       </c>
       <c r="AN235" t="n">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AO235" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="AP235" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ235" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR235" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AS235" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AT235" t="n">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="AU235" t="n">
         <v>4</v>
@@ -51917,25 +51917,25 @@
         <v>2.05</v>
       </c>
       <c r="AN236" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AO236" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AP236" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR236" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AS236" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AT236" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AU236" t="n">
         <v>2</v>
@@ -52135,25 +52135,25 @@
         <v>1.44</v>
       </c>
       <c r="AN237" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AO237" t="n">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AP237" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ237" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR237" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AS237" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AT237" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="AU237" t="n">
         <v>4</v>
@@ -52353,25 +52353,25 @@
         <v>1.58</v>
       </c>
       <c r="AN238" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AO238" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ238" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR238" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AS238" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AT238" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="AU238" t="n">
         <v>2</v>
@@ -52571,25 +52571,25 @@
         <v>1.58</v>
       </c>
       <c r="AN239" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AO239" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AP239" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR239" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AS239" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AT239" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AU239" t="n">
         <v>8</v>
@@ -52789,25 +52789,25 @@
         <v>2</v>
       </c>
       <c r="AN240" t="n">
-        <v>1.12</v>
+        <v>0.67</v>
       </c>
       <c r="AO240" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AP240" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR240" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AS240" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AT240" t="n">
-        <v>2.73</v>
+        <v>2.51</v>
       </c>
       <c r="AU240" t="n">
         <v>4</v>
@@ -53007,25 +53007,25 @@
         <v>1.62</v>
       </c>
       <c r="AN241" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ241" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR241" t="n">
         <v>1.65</v>
       </c>
-      <c r="AO241" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AP241" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ241" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR241" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AS241" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT241" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AU241" t="n">
         <v>7</v>
@@ -53225,25 +53225,25 @@
         <v>1.52</v>
       </c>
       <c r="AN242" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AO242" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AP242" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ242" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR242" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AS242" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AT242" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AU242" t="n">
         <v>7</v>
@@ -53446,22 +53446,22 @@
         <v>1</v>
       </c>
       <c r="AO243" t="n">
-        <v>0.88</v>
+        <v>0.54</v>
       </c>
       <c r="AP243" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ243" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR243" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AS243" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AT243" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="AU243" t="n">
         <v>3</v>
@@ -53661,25 +53661,25 @@
         <v>1.32</v>
       </c>
       <c r="AN244" t="n">
-        <v>0.62</v>
+        <v>1.15</v>
       </c>
       <c r="AO244" t="n">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AP244" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ244" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR244" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AS244" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AT244" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AU244" t="n">
         <v>4</v>
@@ -53879,25 +53879,25 @@
         <v>1.46</v>
       </c>
       <c r="AN245" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AO245" t="n">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="AP245" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ245" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR245" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS245" t="n">
         <v>1.31</v>
       </c>
-      <c r="AS245" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AT245" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AU245" t="n">
         <v>4</v>
@@ -54097,25 +54097,25 @@
         <v>1.29</v>
       </c>
       <c r="AN246" t="n">
-        <v>0.89</v>
+        <v>1.23</v>
       </c>
       <c r="AO246" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AP246" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ246" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR246" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AS246" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AT246" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="AU246" t="n">
         <v>5</v>
@@ -54315,25 +54315,25 @@
         <v>2.17</v>
       </c>
       <c r="AN247" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AO247" t="n">
         <v>1.15</v>
       </c>
-      <c r="AO247" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AP247" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ247" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR247" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS247" t="n">
         <v>1.15</v>
       </c>
-      <c r="AR247" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS247" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AT247" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="AU247" t="n">
         <v>4</v>
@@ -54533,25 +54533,25 @@
         <v>1.92</v>
       </c>
       <c r="AN248" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AO248" t="n">
         <v>1</v>
       </c>
       <c r="AP248" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ248" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR248" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AS248" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AT248" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="AU248" t="n">
         <v>4</v>
@@ -54751,25 +54751,25 @@
         <v>1.26</v>
       </c>
       <c r="AN249" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AO249" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AP249" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR249" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AS249" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AT249" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="AU249" t="n">
         <v>4</v>
@@ -54972,22 +54972,22 @@
         <v>1.85</v>
       </c>
       <c r="AO250" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AP250" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ250" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR250" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AS250" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AT250" t="n">
-        <v>2.98</v>
+        <v>3.13</v>
       </c>
       <c r="AU250" t="n">
         <v>4</v>
@@ -55187,25 +55187,25 @@
         <v>1.82</v>
       </c>
       <c r="AN251" t="n">
-        <v>1.59</v>
+        <v>1</v>
       </c>
       <c r="AO251" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AP251" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ251" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR251" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AS251" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AT251" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="AU251" t="n">
         <v>4</v>
@@ -55405,25 +55405,25 @@
         <v>1.85</v>
       </c>
       <c r="AN252" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AO252" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="AP252" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ252" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR252" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AS252" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AT252" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AU252" t="n">
         <v>5</v>
@@ -55623,25 +55623,25 @@
         <v>2.6</v>
       </c>
       <c r="AN253" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AO253" t="n">
-        <v>0.7</v>
+        <v>0.08</v>
       </c>
       <c r="AP253" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ253" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR253" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AS253" t="n">
         <v>1.11</v>
       </c>
       <c r="AT253" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AU253" t="n">
         <v>7</v>
@@ -55841,25 +55841,25 @@
         <v>2.85</v>
       </c>
       <c r="AN254" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AO254" t="n">
-        <v>0.96</v>
+        <v>0.57</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ254" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR254" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AS254" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AT254" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AU254" t="n">
         <v>5</v>
@@ -56059,25 +56059,25 @@
         <v>1.34</v>
       </c>
       <c r="AN255" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AO255" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AP255" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR255" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AS255" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT255" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AU255" t="n">
         <v>8</v>
@@ -56277,25 +56277,25 @@
         <v>1.61</v>
       </c>
       <c r="AN256" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AO256" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AP256" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ256" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR256" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ256" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR256" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AS256" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AT256" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AU256" t="n">
         <v>3</v>
@@ -56495,22 +56495,22 @@
         <v>1.73</v>
       </c>
       <c r="AN257" t="n">
-        <v>1.25</v>
+        <v>0.85</v>
       </c>
       <c r="AO257" t="n">
-        <v>1.21</v>
+        <v>0.86</v>
       </c>
       <c r="AP257" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR257" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AS257" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AT257" t="n">
         <v>2.95</v>
@@ -56713,25 +56713,25 @@
         <v>1.3</v>
       </c>
       <c r="AN258" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AO258" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AP258" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ258" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR258" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AS258" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT258" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="AU258" t="n">
         <v>4</v>
@@ -56931,25 +56931,25 @@
         <v>1.72</v>
       </c>
       <c r="AN259" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ259" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR259" t="n">
         <v>1.64</v>
       </c>
-      <c r="AO259" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AP259" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ259" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR259" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AS259" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AT259" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="AU259" t="n">
         <v>11</v>
@@ -57149,25 +57149,25 @@
         <v>2</v>
       </c>
       <c r="AN260" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AO260" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AP260" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ260" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AR260" t="n">
         <v>1.62</v>
       </c>
-      <c r="AQ260" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR260" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AS260" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AT260" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="AU260" t="n">
         <v>7</v>
@@ -57367,25 +57367,25 @@
         <v>1.58</v>
       </c>
       <c r="AN261" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AO261" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR261" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AS261" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AT261" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="AU261" t="n">
         <v>5</v>
@@ -57585,25 +57585,25 @@
         <v>1.25</v>
       </c>
       <c r="AN262" t="n">
-        <v>0.68</v>
+        <v>1.29</v>
       </c>
       <c r="AO262" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AP262" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ262" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR262" t="n">
         <v>1.11</v>
       </c>
       <c r="AS262" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AT262" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="AU262" t="n">
         <v>6</v>
@@ -57803,25 +57803,25 @@
         <v>0</v>
       </c>
       <c r="AN263" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AO263" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="AP263" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ263" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR263" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AS263" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AT263" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AU263" t="n">
         <v>5</v>
@@ -58021,25 +58021,25 @@
         <v>0</v>
       </c>
       <c r="AN264" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AO264" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AP264" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ264" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR264" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AS264" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AT264" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AU264" t="n">
         <v>2</v>
@@ -58239,25 +58239,25 @@
         <v>0</v>
       </c>
       <c r="AN265" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AO265" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AP265" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ265" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR265" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AS265" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AT265" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AU265" t="n">
         <v>5</v>
@@ -58457,25 +58457,25 @@
         <v>1.4</v>
       </c>
       <c r="AN266" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AO266" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AP266" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ266" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR266" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AS266" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AT266" t="n">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="AU266" t="n">
         <v>3</v>
@@ -58675,25 +58675,25 @@
         <v>1.33</v>
       </c>
       <c r="AN267" t="n">
-        <v>0.9</v>
+        <v>1.14</v>
       </c>
       <c r="AO267" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="AP267" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR267" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AS267" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AT267" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="AU267" t="n">
         <v>3</v>
@@ -58893,25 +58893,25 @@
         <v>2.88</v>
       </c>
       <c r="AN268" t="n">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="AO268" t="n">
-        <v>0.76</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AP268" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ268" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR268" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AS268" t="n">
         <v>1.12</v>
       </c>
       <c r="AT268" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AU268" t="n">
         <v>6</v>
@@ -59111,25 +59111,25 @@
         <v>1.67</v>
       </c>
       <c r="AN269" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AO269" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ269" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR269" t="n">
         <v>1.5</v>
       </c>
       <c r="AS269" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AT269" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AU269" t="n">
         <v>7</v>
@@ -59329,25 +59329,25 @@
         <v>2.25</v>
       </c>
       <c r="AN270" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AO270" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="AP270" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR270" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AS270" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT270" t="n">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="AU270" t="n">
         <v>8</v>
@@ -59547,25 +59547,25 @@
         <v>1.62</v>
       </c>
       <c r="AN271" t="n">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="AO271" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AP271" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ271" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR271" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AS271" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AT271" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="AU271" t="n">
         <v>4</v>
@@ -59765,25 +59765,25 @@
         <v>0</v>
       </c>
       <c r="AN272" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO272" t="n">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="AP272" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS272" t="n">
         <v>1.15</v>
       </c>
-      <c r="AQ272" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AR272" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS272" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AT272" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AU272" t="n">
         <v>3</v>
@@ -59983,25 +59983,25 @@
         <v>0</v>
       </c>
       <c r="AN273" t="n">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="AO273" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AP273" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ273" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="AR273" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AS273" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AT273" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="AU273" t="n">
         <v>5</v>
@@ -60201,25 +60201,25 @@
         <v>0</v>
       </c>
       <c r="AN274" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AO274" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AQ274" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR274" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AS274" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT274" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AU274" t="n">
         <v>2</v>
@@ -60419,22 +60419,22 @@
         <v>0</v>
       </c>
       <c r="AN275" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AO275" t="n">
-        <v>1.27</v>
+        <v>0.87</v>
       </c>
       <c r="AP275" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ275" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR275" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AS275" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AT275" t="n">
         <v>2.71</v>
@@ -60637,25 +60637,25 @@
         <v>0</v>
       </c>
       <c r="AN276" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO276" t="n">
         <v>0.73</v>
       </c>
-      <c r="AO276" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AP276" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ276" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR276" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AS276" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AT276" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AU276" t="n">
         <v>3</v>
@@ -60855,25 +60855,25 @@
         <v>0</v>
       </c>
       <c r="AN277" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AO277" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="AP277" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ277" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR277" t="n">
         <v>1.41</v>
       </c>
-      <c r="AR277" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AS277" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AT277" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AU277" t="n">
         <v>9</v>
@@ -61073,25 +61073,25 @@
         <v>0</v>
       </c>
       <c r="AN278" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AO278" t="n">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AP278" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ278" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR278" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AS278" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AT278" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AU278" t="n">
         <v>5</v>
@@ -61291,25 +61291,25 @@
         <v>0</v>
       </c>
       <c r="AN279" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="AO279" t="n">
         <v>1.8</v>
       </c>
       <c r="AP279" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ279" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR279" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AS279" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AT279" t="n">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="AU279" t="n">
         <v>7</v>
@@ -61509,25 +61509,25 @@
         <v>0</v>
       </c>
       <c r="AN280" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AO280" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AP280" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ280" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR280" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AS280" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AT280" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="AU280" t="n">
         <v>11</v>
@@ -61727,25 +61727,25 @@
         <v>2.7</v>
       </c>
       <c r="AN281" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="AO281" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="AP281" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR281" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AS281" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT281" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="AU281" t="n">
         <v>4</v>
@@ -61945,25 +61945,25 @@
         <v>1.38</v>
       </c>
       <c r="AN282" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AO282" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AP282" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ282" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AR282" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AS282" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AT282" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="AU282" t="n">
         <v>3</v>
@@ -62163,22 +62163,22 @@
         <v>1.42</v>
       </c>
       <c r="AN283" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="AO283" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="AP283" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ283" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR283" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AS283" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AT283" t="n">
         <v>2.65</v>
@@ -62381,25 +62381,25 @@
         <v>1.42</v>
       </c>
       <c r="AN284" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AO284" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AP284" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ284" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR284" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AS284" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AT284" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AU284" t="n">
         <v>5</v>
@@ -62599,25 +62599,25 @@
         <v>1.4</v>
       </c>
       <c r="AN285" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AO285" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AP285" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ285" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR285" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AS285" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AT285" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="AU285" t="n">
         <v>3</v>
@@ -62817,25 +62817,25 @@
         <v>3.4</v>
       </c>
       <c r="AN286" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AO286" t="n">
-        <v>0.74</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AP286" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ286" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR286" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AS286" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT286" t="n">
-        <v>2.68</v>
+        <v>2.87</v>
       </c>
       <c r="AU286" t="n">
         <v>4</v>
@@ -63035,25 +63035,25 @@
         <v>1.57</v>
       </c>
       <c r="AN287" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AO287" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AP287" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AQ287" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR287" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AS287" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AT287" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AU287" t="n">
         <v>7</v>
@@ -63253,25 +63253,25 @@
         <v>1.25</v>
       </c>
       <c r="AN288" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="AO288" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="AP288" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ288" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR288" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AS288" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AT288" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="AU288" t="n">
         <v>2</v>
@@ -63471,25 +63471,25 @@
         <v>2</v>
       </c>
       <c r="AN289" t="n">
-        <v>1.29</v>
+        <v>0.87</v>
       </c>
       <c r="AO289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ289" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR289" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS289" t="n">
         <v>1.13</v>
       </c>
-      <c r="AP289" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ289" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AR289" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AS289" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AT289" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AU289" t="n">
         <v>4</v>
@@ -63692,22 +63692,22 @@
         <v>1</v>
       </c>
       <c r="AO290" t="n">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="AP290" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AQ290" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="AR290" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AS290" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AT290" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AU290" t="n">
         <v>3</v>
@@ -63907,25 +63907,25 @@
         <v>1.21</v>
       </c>
       <c r="AN291" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AO291" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AP291" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AQ291" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AR291" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AS291" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AT291" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AU291" t="n">
         <v>1</v>
@@ -64125,25 +64125,25 @@
         <v>2</v>
       </c>
       <c r="AN292" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AO292" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AP292" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AQ292" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AR292" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AS292" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT292" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="AU292" t="n">
         <v>8</v>
@@ -64343,25 +64343,25 @@
         <v>1.72</v>
       </c>
       <c r="AN293" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO293" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AP293" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ293" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR293" t="n">
         <v>1.63</v>
       </c>
-      <c r="AO293" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP293" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AQ293" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR293" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AS293" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AT293" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="AU293" t="n">
         <v>4</v>
@@ -64561,22 +64561,22 @@
         <v>2.3</v>
       </c>
       <c r="AN294" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AO294" t="n">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="AP294" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ294" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AR294" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AS294" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AT294" t="n">
         <v>2.58</v>
@@ -64782,22 +64782,22 @@
         <v>1.75</v>
       </c>
       <c r="AO295" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AP295" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AQ295" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="AR295" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AS295" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AT295" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AU295" t="n">
         <v>10</v>
@@ -64997,25 +64997,25 @@
         <v>1.3</v>
       </c>
       <c r="AN296" t="n">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="AO296" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP296" t="n">
-        <v>0.74</v>
+        <v>1.35</v>
       </c>
       <c r="AQ296" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AR296" t="n">
         <v>1.12</v>
       </c>
       <c r="AS296" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AT296" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="AU296" t="n">
         <v>3</v>
@@ -65215,25 +65215,25 @@
         <v>1.82</v>
       </c>
       <c r="AN297" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="AO297" t="n">
-        <v>1.22</v>
+        <v>0.88</v>
       </c>
       <c r="AP297" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AQ297" t="n">
-        <v>1.24</v>
+        <v>0.82</v>
       </c>
       <c r="AR297" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AS297" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AT297" t="n">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="AU297" t="n">
         <v>6</v>
@@ -65433,25 +65433,25 @@
         <v>1.78</v>
       </c>
       <c r="AN298" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AO298" t="n">
-        <v>1.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP298" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AQ298" t="n">
-        <v>1.15</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR298" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AS298" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AT298" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU298" t="n">
         <v>8</v>
@@ -65651,25 +65651,25 @@
         <v>2.1</v>
       </c>
       <c r="AN299" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="AO299" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AP299" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AQ299" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AR299" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AS299" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT299" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AU299" t="n">
         <v>3</v>
@@ -65869,25 +65869,25 @@
         <v>2.4</v>
       </c>
       <c r="AN300" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AO300" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AP300" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AQ300" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AR300" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AS300" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AT300" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="AU300" t="n">
         <v>8</v>
@@ -66087,25 +66087,25 @@
         <v>2.8</v>
       </c>
       <c r="AN301" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="AO301" t="n">
-        <v>0.76</v>
+        <v>0.13</v>
       </c>
       <c r="AP301" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AQ301" t="n">
-        <v>0.74</v>
+        <v>0.12</v>
       </c>
       <c r="AR301" t="n">
         <v>1.52</v>
       </c>
       <c r="AS301" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AT301" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="AU301" t="n">
         <v>5</v>
@@ -66305,25 +66305,25 @@
         <v>1.2</v>
       </c>
       <c r="AN302" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO302" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP302" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ302" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR302" t="n">
         <v>1.48</v>
       </c>
-      <c r="AO302" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AP302" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AQ302" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR302" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AS302" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AT302" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU302" t="n">
         <v>5</v>
@@ -66523,25 +66523,25 @@
         <v>1.4</v>
       </c>
       <c r="AN303" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AO303" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AP303" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AQ303" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AR303" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AS303" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AT303" t="n">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="AU303" t="n">
         <v>5</v>
@@ -66741,25 +66741,25 @@
         <v>1.85</v>
       </c>
       <c r="AN304" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="AO304" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="AP304" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="AQ304" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AR304" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AS304" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AT304" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AU304" t="n">
         <v>9</v>
@@ -66959,25 +66959,25 @@
         <v>1.18</v>
       </c>
       <c r="AN305" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AO305" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AP305" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AQ305" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AR305" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AS305" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT305" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AU305" t="n">
         <v>2</v>
@@ -67177,25 +67177,25 @@
         <v>1.65</v>
       </c>
       <c r="AN306" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="AO306" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AP306" t="n">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AQ306" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AR306" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AS306" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AT306" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AU306" t="n">
         <v>8</v>
@@ -67395,25 +67395,25 @@
         <v>1.3</v>
       </c>
       <c r="AN307" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AO307" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AP307" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AQ307" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR307" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AS307" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT307" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AU307" t="n">
         <v>2</v>
